--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 2/ДЕМАКС АД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 2/ДЕМАКС АД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="214">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -85,6 +88,111 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-05-24</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1903 София, О5 Царско село</t>
+  </si>
+  <si>
+    <t>1910 О5 Бургас</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1171 Кулата</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
+    <t>1173 Ямбол</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1120 Пловдив Радиново</t>
+  </si>
+  <si>
+    <t>1185 София Дружба 1</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1157 Пловдив Тракия</t>
+  </si>
+  <si>
+    <t>1106 Пловдив В. Априлов</t>
+  </si>
+  <si>
+    <t>1183 София Чепинци</t>
+  </si>
+  <si>
+    <t>1131 София Бояна</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
+  </si>
+  <si>
+    <t>1125 Гоце Делчев</t>
+  </si>
+  <si>
+    <t>1122 София Борис III</t>
+  </si>
+  <si>
+    <t>1192 София, Младост Ал. Малинов</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
     <t>СВ9296ВЕ</t>
   </si>
   <si>
@@ -124,6 +232,9 @@
     <t>СВ4297ТА</t>
   </si>
   <si>
+    <t>СВ2578КК</t>
+  </si>
+  <si>
     <t>78970156027720756</t>
   </si>
   <si>
@@ -163,6 +274,9 @@
     <t>78970156027720772</t>
   </si>
   <si>
+    <t>78970156027720806</t>
+  </si>
+  <si>
     <t>EKO RACING 100</t>
   </si>
   <si>
@@ -172,70 +286,358 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTER</t>
-  </si>
-  <si>
-    <t>15:59</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>10:11</t>
-  </si>
-  <si>
-    <t>19:31</t>
-  </si>
-  <si>
-    <t>11:57</t>
-  </si>
-  <si>
-    <t>15:33</t>
-  </si>
-  <si>
-    <t>13:41</t>
-  </si>
-  <si>
-    <t>13:43</t>
-  </si>
-  <si>
-    <t>09:49</t>
-  </si>
-  <si>
-    <t>15:36</t>
-  </si>
-  <si>
-    <t>09:06</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>17:21</t>
-  </si>
-  <si>
-    <t>10:39</t>
-  </si>
-  <si>
-    <t>08:06</t>
-  </si>
-  <si>
-    <t>20:01</t>
-  </si>
-  <si>
-    <t>14:07</t>
-  </si>
-  <si>
-    <t>20:07</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>17:31</t>
+    <t>DIESEL DOUBLE FILTERED</t>
+  </si>
+  <si>
+    <t>2L SUMMER SCREEN WASH LIQUID</t>
+  </si>
+  <si>
+    <t>JETWASH KÄRCHER BGN 2</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>15:58:00</t>
+  </si>
+  <si>
+    <t>13:50:00</t>
+  </si>
+  <si>
+    <t>15:15:00</t>
+  </si>
+  <si>
+    <t>10:09:00</t>
+  </si>
+  <si>
+    <t>19:31:00</t>
+  </si>
+  <si>
+    <t>11:57:00</t>
+  </si>
+  <si>
+    <t>15:33:00</t>
+  </si>
+  <si>
+    <t>13:40:00</t>
+  </si>
+  <si>
+    <t>13:41:00</t>
+  </si>
+  <si>
+    <t>09:49:00</t>
+  </si>
+  <si>
+    <t>15:35:00</t>
+  </si>
+  <si>
+    <t>09:06:00</t>
+  </si>
+  <si>
+    <t>09:20:00</t>
+  </si>
+  <si>
+    <t>17:21:00</t>
+  </si>
+  <si>
+    <t>10:38:00</t>
+  </si>
+  <si>
+    <t>08:07:00</t>
+  </si>
+  <si>
+    <t>19:59:00</t>
+  </si>
+  <si>
+    <t>14:07:00</t>
+  </si>
+  <si>
+    <t>20:03:00</t>
+  </si>
+  <si>
+    <t>16:25:00</t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>16:28:00</t>
+  </si>
+  <si>
+    <t>11:40:00</t>
+  </si>
+  <si>
+    <t>12:01:00</t>
+  </si>
+  <si>
+    <t>15:08:00</t>
+  </si>
+  <si>
+    <t>14:31:00</t>
+  </si>
+  <si>
+    <t>13:21:00</t>
+  </si>
+  <si>
+    <t>12:11:00</t>
+  </si>
+  <si>
+    <t>11:22:00</t>
+  </si>
+  <si>
+    <t>19:22:00</t>
+  </si>
+  <si>
+    <t>10:02:00</t>
+  </si>
+  <si>
+    <t>15:48:00</t>
+  </si>
+  <si>
+    <t>10:07:00</t>
+  </si>
+  <si>
+    <t>07:44:00</t>
+  </si>
+  <si>
+    <t>15:56:00</t>
+  </si>
+  <si>
+    <t>16:20:00</t>
+  </si>
+  <si>
+    <t>16:26:00</t>
+  </si>
+  <si>
+    <t>20:05:00</t>
+  </si>
+  <si>
+    <t>22:37:00</t>
+  </si>
+  <si>
+    <t>12:39:00</t>
+  </si>
+  <si>
+    <t>13:04:00</t>
+  </si>
+  <si>
+    <t>12:16:00</t>
+  </si>
+  <si>
+    <t>12:35:00</t>
+  </si>
+  <si>
+    <t>11:29:00</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>17:22:00</t>
+  </si>
+  <si>
+    <t>13:11:00</t>
+  </si>
+  <si>
+    <t>18:33:00</t>
+  </si>
+  <si>
+    <t>16:44:00</t>
+  </si>
+  <si>
+    <t>09:25:00</t>
+  </si>
+  <si>
+    <t>16:09:00</t>
+  </si>
+  <si>
+    <t>16:59:00</t>
+  </si>
+  <si>
+    <t>16:16:00</t>
+  </si>
+  <si>
+    <t>22:20:00</t>
+  </si>
+  <si>
+    <t>13:37:00</t>
+  </si>
+  <si>
+    <t>17:06:00</t>
+  </si>
+  <si>
+    <t>3231335661 3231335661</t>
+  </si>
+  <si>
+    <t>3231326330 3231326330</t>
+  </si>
+  <si>
+    <t>3231343105 3231343105</t>
+  </si>
+  <si>
+    <t>3231367636 3231367636</t>
+  </si>
+  <si>
+    <t>3231364442 3231364442</t>
+  </si>
+  <si>
+    <t>3231407597 3231407597</t>
+  </si>
+  <si>
+    <t>3231453141 3231453141</t>
+  </si>
+  <si>
+    <t>3231462035 3231462035</t>
+  </si>
+  <si>
+    <t>3231503822 3231503822</t>
+  </si>
+  <si>
+    <t>3231485594 3231485594</t>
+  </si>
+  <si>
+    <t>3231502941 3231502941</t>
+  </si>
+  <si>
+    <t>3231544123 3231544123</t>
+  </si>
+  <si>
+    <t>3231541103 3231541103</t>
+  </si>
+  <si>
+    <t>3231606410 3231606410</t>
+  </si>
+  <si>
+    <t>3231611937 3231611937</t>
+  </si>
+  <si>
+    <t>3231685128 3231685128</t>
+  </si>
+  <si>
+    <t>3231780519 3231780519</t>
+  </si>
+  <si>
+    <t>3231916733 3231916733</t>
+  </si>
+  <si>
+    <t>3231932851 3231932851</t>
+  </si>
+  <si>
+    <t>3231924412 3231924412</t>
+  </si>
+  <si>
+    <t>3231941100 3231941100</t>
+  </si>
+  <si>
+    <t>3231991491 3231991491</t>
+  </si>
+  <si>
+    <t>3232008417 3232008417</t>
+  </si>
+  <si>
+    <t>3232066773 3232066773</t>
+  </si>
+  <si>
+    <t>3232077760 3232077760</t>
+  </si>
+  <si>
+    <t>3232074296 3232074296</t>
+  </si>
+  <si>
+    <t>3232078165 3232078165</t>
+  </si>
+  <si>
+    <t>3232137899 3232137899</t>
+  </si>
+  <si>
+    <t>3232100259 3232100259</t>
+  </si>
+  <si>
+    <t>3232160455 3232160455</t>
+  </si>
+  <si>
+    <t>3232184687 3232184687</t>
+  </si>
+  <si>
+    <t>3232201818 3232201818</t>
+  </si>
+  <si>
+    <t>3232197103 3232197103</t>
+  </si>
+  <si>
+    <t>3232192509 3232192509</t>
+  </si>
+  <si>
+    <t>3232186615 3232186615</t>
+  </si>
+  <si>
+    <t>3232234753 3232234753</t>
+  </si>
+  <si>
+    <t>3232254105 3232254105</t>
+  </si>
+  <si>
+    <t>3232253081 3232253081</t>
+  </si>
+  <si>
+    <t>3232256656 3232256656</t>
+  </si>
+  <si>
+    <t>3232238563 3232238563</t>
+  </si>
+  <si>
+    <t>3232296609 3232296609</t>
+  </si>
+  <si>
+    <t>3232297628 3232297628</t>
+  </si>
+  <si>
+    <t>3232334848 3232334848</t>
+  </si>
+  <si>
+    <t>3232373661 3232373661</t>
+  </si>
+  <si>
+    <t>3232374218 3232374218</t>
+  </si>
+  <si>
+    <t>3232381581 3232381581</t>
+  </si>
+  <si>
+    <t>3232436478 3232436478</t>
+  </si>
+  <si>
+    <t>3232430818 3232430818</t>
+  </si>
+  <si>
+    <t>3232400767 3232400767</t>
+  </si>
+  <si>
+    <t>3232468522 3232468522</t>
+  </si>
+  <si>
+    <t>3232531063 3232531063</t>
+  </si>
+  <si>
+    <t>3232499443 3232499443</t>
+  </si>
+  <si>
+    <t>3232570555 3232570555</t>
+  </si>
+  <si>
+    <t>3232594305 3232594305</t>
+  </si>
+  <si>
+    <t>3232635873 3232635873</t>
+  </si>
+  <si>
+    <t>3232668111 3232668111</t>
+  </si>
+  <si>
+    <t>3232677193 3232677193</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС АД % ГРУПА 2</t>
@@ -659,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -668,16 +1070,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -717,999 +1120,2777 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1195</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F2">
         <v>18.55</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H2">
         <v>1.73</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>32.09</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.78</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>33.02</v>
       </c>
-      <c r="K2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+      <c r="L2" t="s">
+        <v>95</v>
       </c>
       <c r="M2">
-        <v>65394</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3">
-        <v>1903</v>
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F3">
         <v>31.91</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H3">
         <v>1.73</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>55.2</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.78</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>56.8</v>
       </c>
-      <c r="K3" t="s">
-        <v>54</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+      <c r="L3" t="s">
+        <v>96</v>
       </c>
       <c r="M3">
-        <v>121476</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4">
-        <v>1910</v>
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F4">
         <v>52.52</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4">
         <v>1.73</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>90.86</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.77</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>92.95999999999999</v>
       </c>
-      <c r="K4" t="s">
-        <v>55</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+      <c r="L4" t="s">
+        <v>97</v>
       </c>
       <c r="M4">
-        <v>113298</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5">
-        <v>1101</v>
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="F5">
         <v>34.44</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H5">
         <v>1.43</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>49.25</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.53</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>52.69</v>
       </c>
-      <c r="K5" t="s">
-        <v>56</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
+      <c r="L5" t="s">
+        <v>98</v>
       </c>
       <c r="M5">
-        <v>260654</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>1171</v>
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F6">
         <v>42.7</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6">
         <v>1.73</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>73.87</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.78</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>76.01000000000001</v>
       </c>
-      <c r="K6" t="s">
-        <v>57</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+      <c r="L6" t="s">
+        <v>99</v>
       </c>
       <c r="M6">
-        <v>146396</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>1152</v>
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F7">
         <v>38.86</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H7">
         <v>1.73</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>67.23</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.77</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>68.78</v>
       </c>
-      <c r="K7" t="s">
-        <v>58</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+      <c r="L7" t="s">
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>190184</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8">
-        <v>1152</v>
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F8">
         <v>27.68</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8">
         <v>1.73</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>47.89</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.77</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>48.99</v>
       </c>
-      <c r="K8" t="s">
-        <v>59</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
+      <c r="L8" t="s">
+        <v>101</v>
       </c>
       <c r="M8">
-        <v>190927</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9">
-        <v>1173</v>
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="F9">
         <v>24.05</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9">
         <v>1.43</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>34.39</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.52</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>36.56</v>
       </c>
-      <c r="K9" t="s">
-        <v>60</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
+      <c r="L9" t="s">
+        <v>102</v>
       </c>
       <c r="M9">
-        <v>71002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10">
-        <v>1101</v>
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F10">
         <v>49.89</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10">
         <v>1.73</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>86.31</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.79</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>89.3</v>
       </c>
-      <c r="K10" t="s">
-        <v>61</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="L10" t="s">
+        <v>103</v>
       </c>
       <c r="M10">
-        <v>152680</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11">
-        <v>1152</v>
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F11">
         <v>26.24</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11">
         <v>1.73</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>45.4</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.78</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>46.71</v>
       </c>
-      <c r="K11" t="s">
-        <v>62</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
+      <c r="L11" t="s">
+        <v>104</v>
       </c>
       <c r="M11">
-        <v>191243</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12">
-        <v>1902</v>
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F12">
         <v>52.29</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12">
         <v>1.73</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>90.45999999999999</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.79</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>93.59999999999999</v>
       </c>
-      <c r="K12" t="s">
-        <v>63</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
+      <c r="L12" t="s">
+        <v>105</v>
       </c>
       <c r="M12">
-        <v>80360</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13">
-        <v>1120</v>
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F13">
         <v>29.75</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13">
         <v>1.73</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>51.47</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.79</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>53.25</v>
       </c>
-      <c r="K13" t="s">
-        <v>64</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
+      <c r="L13" t="s">
+        <v>106</v>
       </c>
       <c r="M13">
-        <v>187680</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14">
-        <v>1902</v>
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="F14">
         <v>29.78</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>93</v>
+      </c>
+      <c r="H14">
         <v>1.43</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>42.59</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.54</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>45.86</v>
       </c>
-      <c r="K14" t="s">
-        <v>65</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
+      <c r="L14" t="s">
+        <v>107</v>
       </c>
       <c r="M14">
-        <v>80577</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15">
-        <v>1185</v>
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="F15">
         <v>43</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15">
         <v>1.65</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="1">
         <v>70.95</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>1.79</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>76.97</v>
       </c>
-      <c r="K15" t="s">
-        <v>66</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
+      <c r="L15" t="s">
+        <v>108</v>
       </c>
       <c r="M15">
-        <v>144370</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>138800</v>
+      </c>
+      <c r="N15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16">
-        <v>1902</v>
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F16">
         <v>25.54</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16">
         <v>1.74</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>44.44</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>1.79</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>45.72</v>
       </c>
-      <c r="K16" t="s">
-        <v>67</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
+      <c r="L16" t="s">
+        <v>109</v>
       </c>
       <c r="M16">
-        <v>81042</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17">
-        <v>1184</v>
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="F17">
         <v>41.35</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17">
+        <v>1.87</v>
+      </c>
+      <c r="I17" s="1">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="J17">
         <v>2.04</v>
       </c>
-      <c r="H17">
+      <c r="K17" s="1">
         <v>84.34999999999999</v>
       </c>
-      <c r="I17" s="1">
-        <v>2.04</v>
-      </c>
-      <c r="J17">
-        <v>84.34999999999999</v>
-      </c>
-      <c r="K17" t="s">
-        <v>68</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
+      <c r="L17" t="s">
+        <v>110</v>
       </c>
       <c r="M17">
-        <v>496281</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18">
-        <v>1195</v>
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F18">
         <v>48.01</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18">
         <v>1.76</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>84.5</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18">
         <v>1.8</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="1">
         <v>86.42</v>
       </c>
-      <c r="K18" t="s">
-        <v>69</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
+      <c r="L18" t="s">
+        <v>111</v>
       </c>
       <c r="M18">
-        <v>230119</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19">
-        <v>1101</v>
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F19">
         <v>38.97</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19">
         <v>1.77</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="1">
         <v>68.98</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>1.8</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>70.15000000000001</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
+        <v>112</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" t="s">
         <v>70</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>155683</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20">
-        <v>1157</v>
-      </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="F20">
         <v>32.48</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" t="s">
+        <v>93</v>
+      </c>
+      <c r="H20">
         <v>1.48</v>
       </c>
-      <c r="H20">
+      <c r="I20" s="1">
         <v>48.07</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20">
         <v>1.55</v>
       </c>
-      <c r="J20">
+      <c r="K20" s="1">
         <v>50.34</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
+        <v>113</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
         <v>71</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>233261</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21">
-        <v>1902</v>
-      </c>
-      <c r="C21" t="s">
-        <v>35</v>
-      </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="F21">
         <v>20.29</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21">
         <v>1.48</v>
       </c>
-      <c r="H21">
+      <c r="I21" s="1">
         <v>30.03</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21">
         <v>1.55</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="1">
         <v>31.45</v>
       </c>
-      <c r="K21" t="s">
-        <v>72</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
+      <c r="L21" t="s">
+        <v>114</v>
       </c>
       <c r="M21">
-        <v>83381</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
-        <v>1910</v>
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="F22">
         <v>55.69</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22">
         <v>1.77</v>
       </c>
-      <c r="H22">
+      <c r="I22" s="1">
         <v>98.56999999999999</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22">
         <v>1.77</v>
       </c>
-      <c r="J22">
+      <c r="K22" s="1">
         <v>98.56999999999999</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
+        <v>115</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23">
+        <v>49.25</v>
+      </c>
+      <c r="G23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23">
+        <v>1.77</v>
+      </c>
+      <c r="I23" s="1">
+        <v>87.17</v>
+      </c>
+      <c r="J23">
+        <v>1.81</v>
+      </c>
+      <c r="K23" s="1">
+        <v>89.14</v>
+      </c>
+      <c r="L23" t="s">
+        <v>116</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24">
+        <v>23.56</v>
+      </c>
+      <c r="G24" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24">
+        <v>1.77</v>
+      </c>
+      <c r="I24" s="1">
+        <v>41.7</v>
+      </c>
+      <c r="J24">
+        <v>1.8</v>
+      </c>
+      <c r="K24" s="1">
+        <v>42.41</v>
+      </c>
+      <c r="L24" t="s">
+        <v>117</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25">
+        <v>35.33</v>
+      </c>
+      <c r="G25" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25">
+        <v>1.48</v>
+      </c>
+      <c r="I25" s="1">
+        <v>52.29</v>
+      </c>
+      <c r="J25">
+        <v>1.55</v>
+      </c>
+      <c r="K25" s="1">
+        <v>54.76</v>
+      </c>
+      <c r="L25" t="s">
+        <v>118</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26">
+        <v>21.47</v>
+      </c>
+      <c r="G26" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26">
+        <v>1.49</v>
+      </c>
+      <c r="I26" s="1">
+        <v>31.99</v>
+      </c>
+      <c r="J26">
+        <v>1.56</v>
+      </c>
+      <c r="K26" s="1">
+        <v>33.49</v>
+      </c>
+      <c r="L26" t="s">
+        <v>119</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27">
+        <v>62.22</v>
+      </c>
+      <c r="G27" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27">
+        <v>1.78</v>
+      </c>
+      <c r="I27" s="1">
+        <v>110.75</v>
+      </c>
+      <c r="J27">
+        <v>1.8</v>
+      </c>
+      <c r="K27" s="1">
+        <v>112</v>
+      </c>
+      <c r="L27" t="s">
+        <v>120</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F28">
+        <v>48.94</v>
+      </c>
+      <c r="G28" t="s">
+        <v>93</v>
+      </c>
+      <c r="H28">
+        <v>1.63</v>
+      </c>
+      <c r="I28" s="1">
+        <v>79.77</v>
+      </c>
+      <c r="J28">
+        <v>1.76</v>
+      </c>
+      <c r="K28" s="1">
+        <v>86.13</v>
+      </c>
+      <c r="L28" t="s">
+        <v>121</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" t="s">
+        <v>88</v>
+      </c>
+      <c r="F29">
+        <v>28.3</v>
+      </c>
+      <c r="G29" t="s">
+        <v>93</v>
+      </c>
+      <c r="H29">
+        <v>1.49</v>
+      </c>
+      <c r="I29" s="1">
+        <v>42.17</v>
+      </c>
+      <c r="J29">
+        <v>1.59</v>
+      </c>
+      <c r="K29" s="1">
+        <v>45</v>
+      </c>
+      <c r="L29" t="s">
+        <v>122</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30">
+        <v>38.16</v>
+      </c>
+      <c r="G30" t="s">
+        <v>93</v>
+      </c>
+      <c r="H30">
+        <v>1.87</v>
+      </c>
+      <c r="I30" s="1">
+        <v>71.36</v>
+      </c>
+      <c r="J30">
+        <v>2</v>
+      </c>
+      <c r="K30" s="1">
+        <v>76.31999999999999</v>
+      </c>
+      <c r="L30" t="s">
+        <v>123</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31">
+        <v>18.35</v>
+      </c>
+      <c r="G31" t="s">
+        <v>93</v>
+      </c>
+      <c r="H31">
+        <v>1.78</v>
+      </c>
+      <c r="I31" s="1">
+        <v>32.66</v>
+      </c>
+      <c r="J31">
+        <v>1.82</v>
+      </c>
+      <c r="K31" s="1">
+        <v>33.4</v>
+      </c>
+      <c r="L31" t="s">
+        <v>124</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32">
+        <v>31.26</v>
+      </c>
+      <c r="G32" t="s">
+        <v>93</v>
+      </c>
+      <c r="H32">
+        <v>1.49</v>
+      </c>
+      <c r="I32" s="1">
+        <v>46.58</v>
+      </c>
+      <c r="J32">
+        <v>1.58</v>
+      </c>
+      <c r="K32" s="1">
+        <v>49.39</v>
+      </c>
+      <c r="L32" t="s">
+        <v>125</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" t="s">
         <v>73</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>115815</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="3" t="s">
+      <c r="E33" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33">
+        <v>31.15</v>
+      </c>
+      <c r="G33" t="s">
+        <v>93</v>
+      </c>
+      <c r="H33">
+        <v>1.78</v>
+      </c>
+      <c r="I33" s="1">
+        <v>55.45</v>
+      </c>
+      <c r="J33">
+        <v>1.83</v>
+      </c>
+      <c r="K33" s="1">
+        <v>57</v>
+      </c>
+      <c r="L33" t="s">
+        <v>126</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34">
+        <v>50</v>
+      </c>
+      <c r="G34" t="s">
+        <v>93</v>
+      </c>
+      <c r="H34">
+        <v>1.63</v>
+      </c>
+      <c r="I34" s="1">
+        <v>81.5</v>
+      </c>
+      <c r="J34">
+        <v>1.75</v>
+      </c>
+      <c r="K34" s="1">
+        <v>87.5</v>
+      </c>
+      <c r="L34" t="s">
+        <v>127</v>
+      </c>
+      <c r="M34">
+        <v>139000</v>
+      </c>
+      <c r="N34" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="4" t="s">
+      <c r="E35" t="s">
+        <v>87</v>
+      </c>
+      <c r="F35">
+        <v>26</v>
+      </c>
+      <c r="G35" t="s">
+        <v>93</v>
+      </c>
+      <c r="H35">
+        <v>1.78</v>
+      </c>
+      <c r="I35" s="1">
+        <v>46.28</v>
+      </c>
+      <c r="J35">
+        <v>1.82</v>
+      </c>
+      <c r="K35" s="1">
+        <v>47.32</v>
+      </c>
+      <c r="L35" t="s">
+        <v>128</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" t="s">
+        <v>87</v>
+      </c>
+      <c r="F36">
+        <v>45.61</v>
+      </c>
+      <c r="G36" t="s">
+        <v>93</v>
+      </c>
+      <c r="H36">
+        <v>1.78</v>
+      </c>
+      <c r="I36" s="1">
+        <v>81.19</v>
+      </c>
+      <c r="J36">
+        <v>1.82</v>
+      </c>
+      <c r="K36" s="1">
+        <v>83.01000000000001</v>
+      </c>
+      <c r="L36" t="s">
+        <v>129</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F37">
+        <v>17.83</v>
+      </c>
+      <c r="G37" t="s">
+        <v>93</v>
+      </c>
+      <c r="H37">
+        <v>1.49</v>
+      </c>
+      <c r="I37" s="1">
+        <v>26.57</v>
+      </c>
+      <c r="J37">
+        <v>1.57</v>
+      </c>
+      <c r="K37" s="1">
+        <v>27.99</v>
+      </c>
+      <c r="L37" t="s">
+        <v>130</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" t="s">
+        <v>74</v>
+      </c>
+      <c r="E38" t="s">
+        <v>87</v>
+      </c>
+      <c r="F38">
+        <v>17.7</v>
+      </c>
+      <c r="G38" t="s">
+        <v>93</v>
+      </c>
+      <c r="H38">
+        <v>1.78</v>
+      </c>
+      <c r="I38" s="1">
+        <v>31.51</v>
+      </c>
+      <c r="J38">
+        <v>1.82</v>
+      </c>
+      <c r="K38" s="1">
+        <v>32.21</v>
+      </c>
+      <c r="L38" t="s">
+        <v>131</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39" t="s">
+        <v>74</v>
+      </c>
+      <c r="E39" t="s">
+        <v>91</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" t="s">
+        <v>94</v>
+      </c>
+      <c r="H39">
+        <v>4.34</v>
+      </c>
+      <c r="I39" s="1">
+        <v>4.34</v>
+      </c>
+      <c r="J39">
+        <v>4.34</v>
+      </c>
+      <c r="K39" s="1">
+        <v>4.34</v>
+      </c>
+      <c r="L39" t="s">
+        <v>131</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" t="s">
+        <v>87</v>
+      </c>
+      <c r="F40">
+        <v>43</v>
+      </c>
+      <c r="G40" t="s">
+        <v>93</v>
+      </c>
+      <c r="H40">
+        <v>1.78</v>
+      </c>
+      <c r="I40" s="1">
+        <v>76.54000000000001</v>
+      </c>
+      <c r="J40">
+        <v>1.82</v>
+      </c>
+      <c r="K40" s="1">
+        <v>78.26000000000001</v>
+      </c>
+      <c r="L40" t="s">
+        <v>132</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" t="s">
+        <v>87</v>
+      </c>
+      <c r="F41">
+        <v>13.98</v>
+      </c>
+      <c r="G41" t="s">
+        <v>93</v>
+      </c>
+      <c r="H41">
+        <v>1.78</v>
+      </c>
+      <c r="I41" s="1">
+        <v>24.88</v>
+      </c>
+      <c r="J41">
+        <v>1.83</v>
+      </c>
+      <c r="K41" s="1">
+        <v>25.58</v>
+      </c>
+      <c r="L41" t="s">
+        <v>133</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" t="s">
+        <v>78</v>
+      </c>
+      <c r="E42" t="s">
+        <v>87</v>
+      </c>
+      <c r="F42">
+        <v>26.14</v>
+      </c>
+      <c r="G42" t="s">
+        <v>93</v>
+      </c>
+      <c r="H42">
+        <v>1.78</v>
+      </c>
+      <c r="I42" s="1">
+        <v>46.53</v>
+      </c>
+      <c r="J42">
+        <v>1.82</v>
+      </c>
+      <c r="K42" s="1">
+        <v>47.57</v>
+      </c>
+      <c r="L42" t="s">
+        <v>134</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" t="s">
+        <v>64</v>
+      </c>
+      <c r="D43" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43">
+        <v>38.35</v>
+      </c>
+      <c r="G43" t="s">
+        <v>93</v>
+      </c>
+      <c r="H43">
+        <v>1.78</v>
+      </c>
+      <c r="I43" s="1">
+        <v>68.26000000000001</v>
+      </c>
+      <c r="J43">
+        <v>1.82</v>
+      </c>
+      <c r="K43" s="1">
+        <v>69.8</v>
+      </c>
+      <c r="L43" t="s">
+        <v>135</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" t="s">
+        <v>30</v>
+      </c>
+      <c r="B44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" t="s">
+        <v>90</v>
+      </c>
+      <c r="F44">
+        <v>47.68</v>
+      </c>
+      <c r="G44" t="s">
+        <v>93</v>
+      </c>
+      <c r="H44">
+        <v>1.87</v>
+      </c>
+      <c r="I44" s="1">
+        <v>89.16</v>
+      </c>
+      <c r="J44">
+        <v>1.98</v>
+      </c>
+      <c r="K44" s="1">
+        <v>94.41</v>
+      </c>
+      <c r="L44" t="s">
+        <v>136</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45" t="s">
+        <v>73</v>
+      </c>
+      <c r="E45" t="s">
+        <v>87</v>
+      </c>
+      <c r="F45">
+        <v>29.69</v>
+      </c>
+      <c r="G45" t="s">
+        <v>93</v>
+      </c>
+      <c r="H45">
+        <v>1.78</v>
+      </c>
+      <c r="I45" s="1">
+        <v>52.85</v>
+      </c>
+      <c r="J45">
+        <v>1.83</v>
+      </c>
+      <c r="K45" s="1">
+        <v>54.33</v>
+      </c>
+      <c r="L45" t="s">
+        <v>137</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" t="s">
+        <v>32</v>
+      </c>
+      <c r="B46" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" t="s">
+        <v>67</v>
+      </c>
+      <c r="D46" t="s">
+        <v>81</v>
+      </c>
+      <c r="E46" t="s">
+        <v>87</v>
+      </c>
+      <c r="F46">
+        <v>27.97</v>
+      </c>
+      <c r="G46" t="s">
+        <v>93</v>
+      </c>
+      <c r="H46">
+        <v>1.78</v>
+      </c>
+      <c r="I46" s="1">
+        <v>49.79</v>
+      </c>
+      <c r="J46">
+        <v>1.82</v>
+      </c>
+      <c r="K46" s="1">
+        <v>50.91</v>
+      </c>
+      <c r="L46" t="s">
+        <v>138</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D47" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" t="s">
+        <v>92</v>
+      </c>
+      <c r="F47">
+        <v>6</v>
+      </c>
+      <c r="G47" t="s">
+        <v>94</v>
+      </c>
+      <c r="H47">
+        <v>1.02</v>
+      </c>
+      <c r="I47" s="1">
+        <v>6.12</v>
+      </c>
+      <c r="J47">
+        <v>1.02</v>
+      </c>
+      <c r="K47" s="1">
+        <v>6.12</v>
+      </c>
+      <c r="L47" t="s">
+        <v>139</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" t="s">
+        <v>64</v>
+      </c>
+      <c r="D48" t="s">
+        <v>78</v>
+      </c>
+      <c r="E48" t="s">
+        <v>87</v>
+      </c>
+      <c r="F48">
+        <v>46.43</v>
+      </c>
+      <c r="G48" t="s">
+        <v>93</v>
+      </c>
+      <c r="H48">
+        <v>1.78</v>
+      </c>
+      <c r="I48" s="1">
+        <v>82.65000000000001</v>
+      </c>
+      <c r="J48">
+        <v>1.82</v>
+      </c>
+      <c r="K48" s="1">
+        <v>84.5</v>
+      </c>
+      <c r="L48" t="s">
+        <v>140</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D49" t="s">
+        <v>77</v>
+      </c>
+      <c r="E49" t="s">
+        <v>88</v>
+      </c>
+      <c r="F49">
+        <v>39.75</v>
+      </c>
+      <c r="G49" t="s">
+        <v>93</v>
+      </c>
+      <c r="H49">
+        <v>1.49</v>
+      </c>
+      <c r="I49" s="1">
+        <v>59.23</v>
+      </c>
+      <c r="J49">
+        <v>1.57</v>
+      </c>
+      <c r="K49" s="1">
+        <v>62.41</v>
+      </c>
+      <c r="L49" t="s">
+        <v>141</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" t="s">
+        <v>82</v>
+      </c>
+      <c r="E50" t="s">
+        <v>90</v>
+      </c>
+      <c r="F50">
+        <v>61.05</v>
+      </c>
+      <c r="G50" t="s">
+        <v>93</v>
+      </c>
+      <c r="H50">
+        <v>1.87</v>
+      </c>
+      <c r="I50" s="1">
+        <v>114.16</v>
+      </c>
+      <c r="J50">
+        <v>1.98</v>
+      </c>
+      <c r="K50" s="1">
+        <v>120.88</v>
+      </c>
+      <c r="L50" t="s">
+        <v>142</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" t="s">
+        <v>33</v>
+      </c>
+      <c r="B51" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" t="s">
+        <v>62</v>
+      </c>
+      <c r="D51" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="E51" t="s">
+        <v>87</v>
+      </c>
+      <c r="F51">
+        <v>41.03</v>
+      </c>
+      <c r="G51" t="s">
+        <v>93</v>
+      </c>
+      <c r="H51">
+        <v>1.78</v>
+      </c>
+      <c r="I51" s="1">
+        <v>73.03</v>
+      </c>
+      <c r="J51">
+        <v>1.82</v>
+      </c>
+      <c r="K51" s="1">
+        <v>74.67</v>
+      </c>
+      <c r="L51" t="s">
+        <v>143</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52" t="s">
+        <v>84</v>
+      </c>
+      <c r="E52" t="s">
+        <v>88</v>
+      </c>
+      <c r="F52">
+        <v>34.4</v>
+      </c>
+      <c r="G52" t="s">
+        <v>93</v>
+      </c>
+      <c r="H52">
+        <v>1.49</v>
+      </c>
+      <c r="I52" s="1">
+        <v>51.26</v>
+      </c>
+      <c r="J52">
+        <v>1.57</v>
+      </c>
+      <c r="K52" s="1">
+        <v>54.01</v>
+      </c>
+      <c r="L52" t="s">
+        <v>144</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" t="s">
+        <v>82</v>
+      </c>
+      <c r="E53" t="s">
+        <v>90</v>
+      </c>
+      <c r="F53">
+        <v>41.94</v>
+      </c>
+      <c r="G53" t="s">
+        <v>93</v>
+      </c>
+      <c r="H53">
+        <v>1.87</v>
+      </c>
+      <c r="I53" s="1">
+        <v>78.43000000000001</v>
+      </c>
+      <c r="J53">
+        <v>1.98</v>
+      </c>
+      <c r="K53" s="1">
+        <v>83.04000000000001</v>
+      </c>
+      <c r="L53" t="s">
+        <v>145</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" t="s">
+        <v>35</v>
+      </c>
+      <c r="B54" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54" t="s">
+        <v>60</v>
+      </c>
+      <c r="D54" t="s">
+        <v>74</v>
+      </c>
+      <c r="E54" t="s">
+        <v>87</v>
+      </c>
+      <c r="F54">
+        <v>47.54</v>
+      </c>
+      <c r="G54" t="s">
+        <v>93</v>
+      </c>
+      <c r="H54">
+        <v>1.78</v>
+      </c>
+      <c r="I54" s="1">
+        <v>84.62</v>
+      </c>
+      <c r="J54">
+        <v>1.82</v>
+      </c>
+      <c r="K54" s="1">
+        <v>86.52</v>
+      </c>
+      <c r="L54" t="s">
+        <v>146</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" t="s">
+        <v>71</v>
+      </c>
+      <c r="D55" t="s">
+        <v>85</v>
+      </c>
+      <c r="E55" t="s">
+        <v>88</v>
+      </c>
+      <c r="F55">
+        <v>12.1</v>
+      </c>
+      <c r="G55" t="s">
+        <v>93</v>
+      </c>
+      <c r="H55">
+        <v>1.51</v>
+      </c>
+      <c r="I55" s="1">
+        <v>18.27</v>
+      </c>
+      <c r="J55">
+        <v>1.57</v>
+      </c>
+      <c r="K55" s="1">
+        <v>19</v>
+      </c>
+      <c r="L55" t="s">
+        <v>147</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" t="s">
+        <v>85</v>
+      </c>
+      <c r="E56" t="s">
+        <v>91</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
+        <v>94</v>
+      </c>
+      <c r="H56">
+        <v>4.99</v>
+      </c>
+      <c r="I56" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="J56">
+        <v>4.99</v>
+      </c>
+      <c r="K56" s="1">
+        <v>4.99</v>
+      </c>
+      <c r="L56" t="s">
+        <v>147</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" t="s">
+        <v>36</v>
+      </c>
+      <c r="B57" t="s">
+        <v>54</v>
+      </c>
+      <c r="C57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" t="s">
         <v>78</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="6">
-        <v>538.6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>14</v>
-      </c>
-      <c r="D27" s="7">
-        <v>1.7402</v>
-      </c>
-      <c r="E27" s="6">
-        <v>937.27</v>
-      </c>
-      <c r="F27" s="6">
-        <v>960.28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="6">
-        <v>141.04</v>
-      </c>
-      <c r="C28" s="6">
-        <v>5</v>
-      </c>
-      <c r="D28" s="7">
-        <v>1.4487</v>
-      </c>
-      <c r="E28" s="6">
-        <v>204.33</v>
-      </c>
-      <c r="F28" s="6">
-        <v>216.9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="6">
-        <v>43</v>
-      </c>
-      <c r="C29" s="6">
+      <c r="E57" t="s">
+        <v>87</v>
+      </c>
+      <c r="F57">
+        <v>18.81</v>
+      </c>
+      <c r="G57" t="s">
+        <v>93</v>
+      </c>
+      <c r="H57">
+        <v>1.8</v>
+      </c>
+      <c r="I57" s="1">
+        <v>33.86</v>
+      </c>
+      <c r="J57">
+        <v>1.83</v>
+      </c>
+      <c r="K57" s="1">
+        <v>34.42</v>
+      </c>
+      <c r="L57" t="s">
+        <v>148</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" t="s">
+        <v>60</v>
+      </c>
+      <c r="D58" t="s">
+        <v>74</v>
+      </c>
+      <c r="E58" t="s">
+        <v>87</v>
+      </c>
+      <c r="F58">
+        <v>35.17</v>
+      </c>
+      <c r="G58" t="s">
+        <v>93</v>
+      </c>
+      <c r="H58">
+        <v>1.8</v>
+      </c>
+      <c r="I58" s="1">
+        <v>63.31</v>
+      </c>
+      <c r="J58">
+        <v>1.82</v>
+      </c>
+      <c r="K58" s="1">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="L58" t="s">
+        <v>120</v>
+      </c>
+      <c r="M58">
         <v>1</v>
       </c>
-      <c r="D29" s="7">
-        <v>1.65</v>
-      </c>
-      <c r="E29" s="6">
-        <v>70.95</v>
-      </c>
-      <c r="F29" s="6">
-        <v>76.97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="6">
-        <v>41.35</v>
-      </c>
-      <c r="C30" s="6">
+      <c r="N58" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" t="s">
+        <v>47</v>
+      </c>
+      <c r="C59" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" t="s">
+        <v>82</v>
+      </c>
+      <c r="E59" t="s">
+        <v>90</v>
+      </c>
+      <c r="F59">
+        <v>71.16</v>
+      </c>
+      <c r="G59" t="s">
+        <v>93</v>
+      </c>
+      <c r="H59">
+        <v>1.85</v>
+      </c>
+      <c r="I59" s="1">
+        <v>131.65</v>
+      </c>
+      <c r="J59">
+        <v>1.97</v>
+      </c>
+      <c r="K59" s="1">
+        <v>140.19</v>
+      </c>
+      <c r="L59" t="s">
+        <v>149</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" t="s">
+        <v>58</v>
+      </c>
+      <c r="C60" t="s">
+        <v>60</v>
+      </c>
+      <c r="D60" t="s">
+        <v>74</v>
+      </c>
+      <c r="E60" t="s">
+        <v>87</v>
+      </c>
+      <c r="F60">
+        <v>30.47</v>
+      </c>
+      <c r="G60" t="s">
+        <v>93</v>
+      </c>
+      <c r="H60">
+        <v>1.8</v>
+      </c>
+      <c r="I60" s="1">
+        <v>54.85</v>
+      </c>
+      <c r="J60">
+        <v>1.83</v>
+      </c>
+      <c r="K60" s="1">
+        <v>55.76</v>
+      </c>
+      <c r="L60" t="s">
+        <v>150</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B65" s="6">
+        <v>1211.02</v>
+      </c>
+      <c r="C65" s="6">
+        <v>34</v>
+      </c>
+      <c r="D65" s="7">
+        <v>1.7631</v>
+      </c>
+      <c r="E65" s="6">
+        <v>2135.15</v>
+      </c>
+      <c r="F65" s="6">
+        <v>2183.1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B66" s="6">
+        <v>361.48</v>
+      </c>
+      <c r="C66" s="6">
+        <v>13</v>
+      </c>
+      <c r="D66" s="7">
+        <v>1.4736</v>
+      </c>
+      <c r="E66" s="6">
+        <v>532.6900000000001</v>
+      </c>
+      <c r="F66" s="6">
+        <v>562.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B67" s="6">
+        <v>301.34</v>
+      </c>
+      <c r="C67" s="6">
+        <v>6</v>
+      </c>
+      <c r="D67" s="7">
+        <v>1.8653</v>
+      </c>
+      <c r="E67" s="6">
+        <v>562.08</v>
+      </c>
+      <c r="F67" s="6">
+        <v>599.1900000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B68" s="6">
+        <v>141.94</v>
+      </c>
+      <c r="C68" s="6">
+        <v>3</v>
+      </c>
+      <c r="D68" s="7">
+        <v>1.636</v>
+      </c>
+      <c r="E68" s="6">
+        <v>232.22</v>
+      </c>
+      <c r="F68" s="6">
+        <v>250.6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B69" s="6">
+        <v>6</v>
+      </c>
+      <c r="C69" s="6">
         <v>1</v>
       </c>
-      <c r="D30" s="7">
-        <v>2.0399</v>
-      </c>
-      <c r="E30" s="6">
-        <v>84.34999999999999</v>
-      </c>
-      <c r="F30" s="6">
-        <v>84.34999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="9">
-        <v>763.99</v>
-      </c>
-      <c r="C31" s="9">
-        <v>21</v>
-      </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="9">
-        <v>1296.9</v>
-      </c>
-      <c r="F31" s="9">
-        <v>1338.5</v>
+      <c r="D69" s="7">
+        <v>1.02</v>
+      </c>
+      <c r="E69" s="6">
+        <v>6.12</v>
+      </c>
+      <c r="F69" s="6">
+        <v>6.12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B70" s="6">
+        <v>2</v>
+      </c>
+      <c r="C70" s="6">
+        <v>2</v>
+      </c>
+      <c r="D70" s="7">
+        <v>4.665</v>
+      </c>
+      <c r="E70" s="6">
+        <v>9.33</v>
+      </c>
+      <c r="F70" s="6">
+        <v>9.33</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B71" s="9">
+        <v>2023.78</v>
+      </c>
+      <c r="C71" s="9">
+        <v>59</v>
+      </c>
+      <c r="D71" s="7"/>
+      <c r="E71" s="9">
+        <v>3477.59</v>
+      </c>
+      <c r="F71" s="9">
+        <v>3611.29</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A63:F63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 2/ДЕМАКС АД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 2/ДЕМАКС АД % ГРУПА 2.xlsx
@@ -691,7 +691,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -701,12 +701,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -756,17 +750,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 2/ДЕМАКС АД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 2/ДЕМАКС АД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="205">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-01</t>
   </si>
   <si>
@@ -91,49 +97,124 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>Хасково</t>
-  </si>
-  <si>
-    <t>Ахелой</t>
-  </si>
-  <si>
-    <t>София Дружба 2</t>
-  </si>
-  <si>
-    <t>Свиленград</t>
-  </si>
-  <si>
-    <t>София Бояна</t>
-  </si>
-  <si>
-    <t>Ихтиман</t>
-  </si>
-  <si>
-    <t>София Малинов</t>
-  </si>
-  <si>
-    <t>София Малинова Долина</t>
-  </si>
-  <si>
-    <t>АМ Тракия</t>
-  </si>
-  <si>
-    <t>Кулата Струма</t>
-  </si>
-  <si>
-    <t>Ямбол</t>
-  </si>
-  <si>
-    <t>София Царско Село</t>
-  </si>
-  <si>
-    <t>София Младост</t>
-  </si>
-  <si>
-    <t>Велинград</t>
-  </si>
-  <si>
-    <t>Кулата</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1909 О5, Хасково</t>
+  </si>
+  <si>
+    <t>1916 О5 Ахелой</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1131 София Бояна</t>
+  </si>
+  <si>
+    <t>1177 Свиленград</t>
+  </si>
+  <si>
+    <t>1192 София, Младост Ал. Малинов</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
+    <t>1173 Ямбол</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
+  </si>
+  <si>
+    <t>1903 София, О5 Царско село</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
+    <t>1137 Велинград</t>
+  </si>
+  <si>
+    <t>1171 Кулата</t>
+  </si>
+  <si>
+    <t>1132 Хасково Левски</t>
+  </si>
+  <si>
+    <t>1157 Пловдив Тракия</t>
+  </si>
+  <si>
+    <t>1186 Севлиево</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
+    <t>1118 Сливен Била</t>
+  </si>
+  <si>
+    <t>1160 София бул. България</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1914 О5, Плевен</t>
+  </si>
+  <si>
+    <t>1918 O5 Търговище</t>
+  </si>
+  <si>
+    <t>1910 О5 Бургас</t>
+  </si>
+  <si>
+    <t>1185 София Дружба 1</t>
   </si>
   <si>
     <t>СВ4298ТА</t>
@@ -142,60 +223,84 @@
     <t>СВ0660ТР</t>
   </si>
   <si>
+    <t>СВ2578КК</t>
+  </si>
+  <si>
+    <t>СВ7717МО</t>
+  </si>
+  <si>
     <t>СВ0481НН</t>
   </si>
   <si>
-    <t>СВ7717МО</t>
-  </si>
-  <si>
-    <t>СВ2578КК</t>
-  </si>
-  <si>
     <t>СВ2104ТЕ</t>
   </si>
   <si>
+    <t>СВ9610НА</t>
+  </si>
+  <si>
     <t>СВ4297ТА</t>
   </si>
   <si>
-    <t>СВ9610НА</t>
-  </si>
-  <si>
     <t>СА5061ХС</t>
   </si>
   <si>
     <t>СВ5666НВ</t>
   </si>
   <si>
+    <t>СВ7887РН</t>
+  </si>
+  <si>
+    <t>СВ1818НО</t>
+  </si>
+  <si>
+    <t>СВ2318ХТ</t>
+  </si>
+  <si>
+    <t>СВ8778ВР</t>
+  </si>
+  <si>
     <t>78970156027720780</t>
   </si>
   <si>
     <t>78970156027720665</t>
   </si>
   <si>
+    <t>78970156027720806</t>
+  </si>
+  <si>
+    <t>78970156027720707</t>
+  </si>
+  <si>
     <t>78970156027720798</t>
   </si>
   <si>
-    <t>78970156027720707</t>
-  </si>
-  <si>
-    <t>78970156027720806</t>
-  </si>
-  <si>
     <t>78970156027720699</t>
   </si>
   <si>
+    <t>78970156027720814</t>
+  </si>
+  <si>
     <t>78970156027720772</t>
   </si>
   <si>
-    <t>78970156027720814</t>
-  </si>
-  <si>
     <t>78970156027720723</t>
   </si>
   <si>
     <t>78970156027720731</t>
   </si>
   <si>
+    <t>78970156027720681</t>
+  </si>
+  <si>
+    <t>78970156027720749</t>
+  </si>
+  <si>
+    <t>78970156027720715</t>
+  </si>
+  <si>
+    <t>78970156027720673</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
@@ -208,88 +313,304 @@
     <t>EKO RACING 100</t>
   </si>
   <si>
-    <t>10 Л. ДOБABKA ADPLUS ДИЗEЛOBИ ДBИГATEЛИ</t>
-  </si>
-  <si>
-    <t>2Л EKO ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ-ГOTOBA</t>
-  </si>
-  <si>
-    <t>2026-07-01 09:26:18</t>
-  </si>
-  <si>
-    <t>2026-07-01 12:06:59</t>
-  </si>
-  <si>
-    <t>2026-07-02 09:19:08</t>
-  </si>
-  <si>
-    <t>2026-07-03 09:02:51</t>
-  </si>
-  <si>
-    <t>2026-07-03 13:23:46</t>
-  </si>
-  <si>
-    <t>2026-07-03 13:56:00</t>
-  </si>
-  <si>
-    <t>2026-07-03 17:50:30</t>
-  </si>
-  <si>
-    <t>2026-07-03 19:10:56</t>
-  </si>
-  <si>
-    <t>2026-07-05 15:54:57</t>
-  </si>
-  <si>
-    <t>2026-07-06 10:21:22</t>
-  </si>
-  <si>
-    <t>2026-07-06 10:46:10</t>
-  </si>
-  <si>
-    <t>2026-07-07 15:35:11</t>
-  </si>
-  <si>
-    <t>2026-07-07 15:35:12</t>
-  </si>
-  <si>
-    <t>2026-07-07 16:18:44</t>
-  </si>
-  <si>
-    <t>2026-07-07 16:18:45</t>
-  </si>
-  <si>
-    <t>2026-07-08 15:52:04</t>
-  </si>
-  <si>
-    <t>2026-07-08 23:00:52</t>
-  </si>
-  <si>
-    <t>2026-07-09 14:39:21</t>
-  </si>
-  <si>
-    <t>2026-07-09 14:39:22</t>
-  </si>
-  <si>
-    <t>2026-07-09 16:41:58</t>
-  </si>
-  <si>
-    <t>2026-07-10 14:21:42</t>
-  </si>
-  <si>
-    <t>2026-07-11 11:03:18</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:32:21</t>
-  </si>
-  <si>
-    <t>2026-07-13 10:48:24</t>
-  </si>
-  <si>
-    <t>2026-07-14 19:28:47</t>
-  </si>
-  <si>
-    <t>2026-07-15 22:27:00</t>
+    <t>10L ADPLUS DIESEL ADDITIVE</t>
+  </si>
+  <si>
+    <t>2L SUMMER SCREEN WASH LIQUID</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>09:25:00</t>
+  </si>
+  <si>
+    <t>12:04:00</t>
+  </si>
+  <si>
+    <t>09:19:00</t>
+  </si>
+  <si>
+    <t>13:55:00</t>
+  </si>
+  <si>
+    <t>13:23:00</t>
+  </si>
+  <si>
+    <t>09:02:00</t>
+  </si>
+  <si>
+    <t>17:50:00</t>
+  </si>
+  <si>
+    <t>19:10:00</t>
+  </si>
+  <si>
+    <t>15:54:00</t>
+  </si>
+  <si>
+    <t>10:45:00</t>
+  </si>
+  <si>
+    <t>10:21:00</t>
+  </si>
+  <si>
+    <t>15:35:00</t>
+  </si>
+  <si>
+    <t>16:19:00</t>
+  </si>
+  <si>
+    <t>15:52:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
+    <t>14:39:00</t>
+  </si>
+  <si>
+    <t>16:38:00</t>
+  </si>
+  <si>
+    <t>14:22:00</t>
+  </si>
+  <si>
+    <t>11:02:00</t>
+  </si>
+  <si>
+    <t>10:48:00</t>
+  </si>
+  <si>
+    <t>10:32:00</t>
+  </si>
+  <si>
+    <t>19:28:00</t>
+  </si>
+  <si>
+    <t>22:28:00</t>
+  </si>
+  <si>
+    <t>19:57:00</t>
+  </si>
+  <si>
+    <t>20:26:00</t>
+  </si>
+  <si>
+    <t>12:47:00</t>
+  </si>
+  <si>
+    <t>12:03:00</t>
+  </si>
+  <si>
+    <t>00:27:00</t>
+  </si>
+  <si>
+    <t>21:07:00</t>
+  </si>
+  <si>
+    <t>18:52:00</t>
+  </si>
+  <si>
+    <t>10:40:00</t>
+  </si>
+  <si>
+    <t>07:59:00</t>
+  </si>
+  <si>
+    <t>12:40:00</t>
+  </si>
+  <si>
+    <t>10:15:00</t>
+  </si>
+  <si>
+    <t>14:54:00</t>
+  </si>
+  <si>
+    <t>17:40:00</t>
+  </si>
+  <si>
+    <t>22:59:00</t>
+  </si>
+  <si>
+    <t>18:47:00</t>
+  </si>
+  <si>
+    <t>12:26:00</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>08:28:00</t>
+  </si>
+  <si>
+    <t>10:44:00</t>
+  </si>
+  <si>
+    <t>18:35:00</t>
+  </si>
+  <si>
+    <t>11:55:00</t>
+  </si>
+  <si>
+    <t>17:32:00</t>
+  </si>
+  <si>
+    <t>11:36:00</t>
+  </si>
+  <si>
+    <t>20:24:00</t>
+  </si>
+  <si>
+    <t>13:09:00</t>
+  </si>
+  <si>
+    <t>3234157984 3234157984</t>
+  </si>
+  <si>
+    <t>3234165628 3234165628</t>
+  </si>
+  <si>
+    <t>3234200607 3234200607</t>
+  </si>
+  <si>
+    <t>3234245999 3234245999</t>
+  </si>
+  <si>
+    <t>3234249107 3234249107</t>
+  </si>
+  <si>
+    <t>3234257638 3234257638</t>
+  </si>
+  <si>
+    <t>3234255761 3234255761</t>
+  </si>
+  <si>
+    <t>3234264743 3234264743</t>
+  </si>
+  <si>
+    <t>3234343772 3234343772</t>
+  </si>
+  <si>
+    <t>3234408508 3234408508</t>
+  </si>
+  <si>
+    <t>3234393329 3234393329</t>
+  </si>
+  <si>
+    <t>3234444185 3234444185</t>
+  </si>
+  <si>
+    <t>3234446063 3234446063</t>
+  </si>
+  <si>
+    <t>3234462184 3234462184</t>
+  </si>
+  <si>
+    <t>3234476431 3234476431</t>
+  </si>
+  <si>
+    <t>3234536780 3234536780</t>
+  </si>
+  <si>
+    <t>3234542711 3234542711</t>
+  </si>
+  <si>
+    <t>3234617335 3234617335</t>
+  </si>
+  <si>
+    <t>3234624617 3234624617</t>
+  </si>
+  <si>
+    <t>3234746902 3234746902</t>
+  </si>
+  <si>
+    <t>3234735248 3234735248</t>
+  </si>
+  <si>
+    <t>3234794846 3234794846</t>
+  </si>
+  <si>
+    <t>3234846974 3234846974</t>
+  </si>
+  <si>
+    <t>3234897451 3234897451</t>
+  </si>
+  <si>
+    <t>3234898467 3234898467</t>
+  </si>
+  <si>
+    <t>3234950496 3234950496</t>
+  </si>
+  <si>
+    <t>3234940580 3234940580</t>
+  </si>
+  <si>
+    <t>3234970647 3234970647</t>
+  </si>
+  <si>
+    <t>3235062823 3235062823</t>
+  </si>
+  <si>
+    <t>3235012991 3235012991</t>
+  </si>
+  <si>
+    <t>3235046891 3235046891</t>
+  </si>
+  <si>
+    <t>3235086972 3235086972</t>
+  </si>
+  <si>
+    <t>3235184109 3235184109</t>
+  </si>
+  <si>
+    <t>3235247982 3235247982</t>
+  </si>
+  <si>
+    <t>3235230307 3235230307</t>
+  </si>
+  <si>
+    <t>3235297571 3235297571</t>
+  </si>
+  <si>
+    <t>3235308719 3235308719</t>
+  </si>
+  <si>
+    <t>3235303843 3235303843</t>
+  </si>
+  <si>
+    <t>3235347911 3235347911</t>
+  </si>
+  <si>
+    <t>3235432235 3235432235</t>
+  </si>
+  <si>
+    <t>3235438260 3235438260</t>
+  </si>
+  <si>
+    <t>3235439772 3235439772</t>
+  </si>
+  <si>
+    <t>3235490875 3235490875</t>
+  </si>
+  <si>
+    <t>3235532029 3235532029</t>
+  </si>
+  <si>
+    <t>3235597282 3235597282</t>
+  </si>
+  <si>
+    <t>3235581159 3235581159</t>
+  </si>
+  <si>
+    <t>3235663901 3235663901</t>
+  </si>
+  <si>
+    <t>3235653075 3235653075</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС АД % ГРУПА 2</t>
@@ -707,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -716,15 +1037,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -761,484 +1084,562 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="F2">
         <v>29.95</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2">
         <v>1.39</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>41.63</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.52</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>45.52</v>
       </c>
-      <c r="K2" t="s">
-        <v>66</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="L2" t="s">
+        <v>103</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="F3">
         <v>18.22</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3">
         <v>1.39</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>25.33</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.5</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>27.33</v>
       </c>
-      <c r="K3" t="s">
-        <v>67</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="L3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F4">
         <v>41.71</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H4">
         <v>1.7</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>70.91</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.77</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>73.83</v>
       </c>
-      <c r="K4" t="s">
-        <v>68</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="L4" t="s">
+        <v>105</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="F5">
-        <v>40</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.43</v>
+        <v>43.86</v>
+      </c>
+      <c r="G5" t="s">
+        <v>101</v>
       </c>
       <c r="H5">
-        <v>57.2</v>
+        <v>1.7</v>
       </c>
       <c r="I5" s="1">
-        <v>1.51</v>
+        <v>74.56</v>
       </c>
       <c r="J5">
-        <v>60.4</v>
-      </c>
-      <c r="K5" t="s">
-        <v>69</v>
-      </c>
-      <c r="L5">
-        <v>141141</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>1.8</v>
+      </c>
+      <c r="K5" s="1">
+        <v>78.95</v>
+      </c>
+      <c r="L5" t="s">
+        <v>106</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="F6">
         <v>27</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6">
         <v>1.39</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>37.53</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.5</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>40.5</v>
       </c>
-      <c r="K6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="L6" t="s">
+        <v>107</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="F7">
-        <v>43.86</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.7</v>
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>101</v>
       </c>
       <c r="H7">
-        <v>74.56</v>
+        <v>1.43</v>
       </c>
       <c r="I7" s="1">
-        <v>1.8</v>
+        <v>57.2</v>
       </c>
       <c r="J7">
-        <v>78.95</v>
-      </c>
-      <c r="K7" t="s">
-        <v>71</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>1.51</v>
+      </c>
+      <c r="K7" s="1">
+        <v>60.4</v>
+      </c>
+      <c r="L7" t="s">
+        <v>108</v>
+      </c>
+      <c r="M7">
+        <v>141141</v>
+      </c>
+      <c r="N7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F8">
         <v>23.13</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>101</v>
+      </c>
+      <c r="H8">
         <v>1.7</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>39.32</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.77</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>40.94</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>109</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
         <v>72</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F9">
         <v>53.35</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9">
         <v>1.71</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>91.23</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.76</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>93.90000000000001</v>
       </c>
-      <c r="K9" t="s">
-        <v>73</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="L9" t="s">
+        <v>110</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F10">
         <v>42.03</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10">
         <v>1.68</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>70.61</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.82</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>76.48999999999999</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
+        <v>111</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11">
+        <v>28</v>
+      </c>
+      <c r="G11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11">
+        <v>1.39</v>
+      </c>
+      <c r="I11" s="1">
+        <v>38.92</v>
+      </c>
+      <c r="J11">
+        <v>1.49</v>
+      </c>
+      <c r="K11" s="1">
+        <v>41.72</v>
+      </c>
+      <c r="L11" t="s">
+        <v>112</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
         <v>74</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11">
+      <c r="D12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12">
         <v>22.68</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G12" t="s">
+        <v>101</v>
+      </c>
+      <c r="H12">
         <v>1.39</v>
       </c>
-      <c r="H11">
+      <c r="I12" s="1">
         <v>31.53</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J12">
         <v>1.51</v>
       </c>
-      <c r="J11">
+      <c r="K12" s="1">
         <v>34.25</v>
       </c>
-      <c r="K11" t="s">
-        <v>75</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12">
-        <v>28</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1.39</v>
-      </c>
-      <c r="H12">
-        <v>38.92</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J12">
-        <v>41.72</v>
-      </c>
-      <c r="K12" t="s">
-        <v>76</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="L12" t="s">
+        <v>113</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="F13">
         <v>27.82</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>101</v>
+      </c>
+      <c r="H13">
         <v>1.44</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>40.06</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.52</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>42.29</v>
       </c>
-      <c r="K13" t="s">
-        <v>77</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="L13" t="s">
+        <v>114</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
-      <c r="G14" s="1">
-        <v>26.83</v>
+      <c r="G14" t="s">
+        <v>102</v>
       </c>
       <c r="H14">
         <v>26.83</v>
@@ -1249,224 +1650,260 @@
       <c r="J14">
         <v>26.83</v>
       </c>
-      <c r="K14" t="s">
-        <v>78</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="K14" s="1">
+        <v>26.83</v>
+      </c>
+      <c r="L14" t="s">
+        <v>114</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15">
+        <v>25.04</v>
+      </c>
+      <c r="G15" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15">
+        <v>1.44</v>
+      </c>
+      <c r="I15" s="1">
+        <v>36.06</v>
+      </c>
+      <c r="J15">
+        <v>1.52</v>
+      </c>
+      <c r="K15" s="1">
+        <v>38.06</v>
+      </c>
+      <c r="L15" t="s">
+        <v>115</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16">
+        <v>4.49</v>
+      </c>
+      <c r="I16" s="1">
+        <v>4.49</v>
+      </c>
+      <c r="J16">
+        <v>4.49</v>
+      </c>
+      <c r="K16" s="1">
+        <v>4.49</v>
+      </c>
+      <c r="L16" t="s">
+        <v>115</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
         <v>48</v>
       </c>
-      <c r="D15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="1">
-        <v>4.49</v>
-      </c>
-      <c r="H15">
-        <v>4.49</v>
-      </c>
-      <c r="I15" s="1">
-        <v>4.49</v>
-      </c>
-      <c r="J15">
-        <v>4.49</v>
-      </c>
-      <c r="K15" t="s">
-        <v>79</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16">
-        <v>25.04</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="H16">
-        <v>36.06</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J16">
-        <v>38.06</v>
-      </c>
-      <c r="K16" t="s">
-        <v>80</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F17">
         <v>40.98</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17">
         <v>1.69</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="1">
         <v>69.26000000000001</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17">
         <v>1.76</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="1">
         <v>72.12</v>
       </c>
-      <c r="K17" t="s">
-        <v>81</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="L17" t="s">
+        <v>116</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="F18">
         <v>26.29</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H18">
         <v>1.39</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>36.54</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18">
         <v>1.5</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="1">
         <v>39.44</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
+        <v>117</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
         <v>82</v>
       </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" t="s">
-        <v>51</v>
-      </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F19">
         <v>35</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H19">
         <v>1.68</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="1">
         <v>58.8</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>1.78</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>62.3</v>
       </c>
-      <c r="K19" t="s">
-        <v>83</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="L19" t="s">
+        <v>118</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
-      <c r="G20" s="1">
-        <v>26.83</v>
+      <c r="G20" t="s">
+        <v>102</v>
       </c>
       <c r="H20">
         <v>26.83</v>
@@ -1477,450 +1914,1642 @@
       <c r="J20">
         <v>26.83</v>
       </c>
-      <c r="K20" t="s">
-        <v>84</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="K20" s="1">
+        <v>26.83</v>
+      </c>
+      <c r="L20" t="s">
+        <v>118</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="F21">
         <v>35.56</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" t="s">
+        <v>101</v>
+      </c>
+      <c r="H21">
         <v>1.39</v>
       </c>
-      <c r="H21">
+      <c r="I21" s="1">
         <v>49.43</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21">
         <v>1.5</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="1">
         <v>53.34</v>
       </c>
-      <c r="K21" t="s">
-        <v>85</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="L21" t="s">
+        <v>119</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F22">
         <v>64.03</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" t="s">
+        <v>101</v>
+      </c>
+      <c r="H22">
         <v>1.68</v>
       </c>
-      <c r="H22">
+      <c r="I22" s="1">
         <v>107.57</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22">
         <v>1.8</v>
       </c>
-      <c r="J22">
+      <c r="K22" s="1">
         <v>115.25</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
+        <v>120</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" t="s">
         <v>86</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" t="s">
-        <v>55</v>
-      </c>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F23">
         <v>50.09</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23">
         <v>1.69</v>
       </c>
-      <c r="H23">
+      <c r="I23" s="1">
         <v>84.65000000000001</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23">
         <v>1.76</v>
       </c>
-      <c r="J23">
+      <c r="K23" s="1">
         <v>88.16</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
         <v>87</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" t="s">
-        <v>51</v>
-      </c>
       <c r="E24" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="F24">
+        <v>27.55</v>
+      </c>
+      <c r="G24" t="s">
+        <v>101</v>
+      </c>
+      <c r="H24">
+        <v>1.39</v>
+      </c>
+      <c r="I24" s="1">
+        <v>38.29</v>
+      </c>
+      <c r="J24">
+        <v>1.49</v>
+      </c>
+      <c r="K24" s="1">
+        <v>41.05</v>
+      </c>
+      <c r="L24" t="s">
+        <v>122</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" t="s">
+        <v>96</v>
+      </c>
+      <c r="F25">
         <v>46.99</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G25" t="s">
+        <v>101</v>
+      </c>
+      <c r="H25">
         <v>1.68</v>
       </c>
-      <c r="H24">
+      <c r="I25" s="1">
         <v>78.94</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J25">
         <v>1.82</v>
       </c>
-      <c r="J24">
+      <c r="K25" s="1">
         <v>85.52</v>
       </c>
-      <c r="K24" t="s">
-        <v>88</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" t="s">
-        <v>57</v>
-      </c>
-      <c r="E25" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25">
-        <v>27.55</v>
-      </c>
-      <c r="G25" s="1">
-        <v>1.39</v>
-      </c>
-      <c r="H25">
-        <v>38.29</v>
-      </c>
-      <c r="I25" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J25">
-        <v>41.05</v>
-      </c>
-      <c r="K25" t="s">
-        <v>89</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="L25" t="s">
+        <v>123</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F26">
         <v>52.62</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" t="s">
+        <v>101</v>
+      </c>
+      <c r="H26">
         <v>1.68</v>
       </c>
-      <c r="H26">
+      <c r="I26" s="1">
         <v>88.40000000000001</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26">
         <v>1.84</v>
       </c>
-      <c r="J26">
+      <c r="K26" s="1">
         <v>96.81999999999999</v>
       </c>
-      <c r="K26" t="s">
-        <v>90</v>
-      </c>
-      <c r="L26">
+      <c r="L26" t="s">
+        <v>124</v>
+      </c>
+      <c r="M26">
         <v>142000</v>
       </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="N26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="E27" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="F27">
         <v>37.76</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" t="s">
+        <v>101</v>
+      </c>
+      <c r="H27">
         <v>1.4</v>
       </c>
-      <c r="H27">
+      <c r="I27" s="1">
         <v>52.86</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27">
         <v>1.51</v>
       </c>
-      <c r="J27">
+      <c r="K27" s="1">
         <v>57.02</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" t="s">
+        <v>125</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28">
+        <v>20.74</v>
+      </c>
+      <c r="G28" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28">
+        <v>1.4</v>
+      </c>
+      <c r="I28" s="1">
+        <v>29.04</v>
+      </c>
+      <c r="J28">
+        <v>1.5</v>
+      </c>
+      <c r="K28" s="1">
+        <v>31.11</v>
+      </c>
+      <c r="L28" t="s">
+        <v>126</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" t="s">
         <v>91</v>
       </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="3" t="s">
+      <c r="E29" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29">
+        <v>32.02</v>
+      </c>
+      <c r="G29" t="s">
+        <v>101</v>
+      </c>
+      <c r="H29">
+        <v>1.69</v>
+      </c>
+      <c r="I29" s="1">
+        <v>54.11</v>
+      </c>
+      <c r="J29">
+        <v>1.78</v>
+      </c>
+      <c r="K29" s="1">
+        <v>57</v>
+      </c>
+      <c r="L29" t="s">
+        <v>127</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" t="s">
         <v>92</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="4" t="s">
+      <c r="E30" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30">
+        <v>27.18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H30">
+        <v>1.68</v>
+      </c>
+      <c r="I30" s="1">
+        <v>45.66</v>
+      </c>
+      <c r="J30">
+        <v>1.89</v>
+      </c>
+      <c r="K30" s="1">
+        <v>51.37</v>
+      </c>
+      <c r="L30" t="s">
+        <v>128</v>
+      </c>
+      <c r="M30">
+        <v>300</v>
+      </c>
+      <c r="N30" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" t="s">
+        <v>86</v>
+      </c>
+      <c r="E31" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31">
+        <v>63.42</v>
+      </c>
+      <c r="G31" t="s">
+        <v>101</v>
+      </c>
+      <c r="H31">
+        <v>1.69</v>
+      </c>
+      <c r="I31" s="1">
+        <v>107.18</v>
+      </c>
+      <c r="J31">
+        <v>1.77</v>
+      </c>
+      <c r="K31" s="1">
+        <v>112.25</v>
+      </c>
+      <c r="L31" t="s">
+        <v>129</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" t="s">
+        <v>96</v>
+      </c>
+      <c r="F32">
+        <v>31.57</v>
+      </c>
+      <c r="G32" t="s">
+        <v>101</v>
+      </c>
+      <c r="H32">
+        <v>1.69</v>
+      </c>
+      <c r="I32" s="1">
+        <v>53.35</v>
+      </c>
+      <c r="J32">
+        <v>1.92</v>
+      </c>
+      <c r="K32" s="1">
+        <v>60.61</v>
+      </c>
+      <c r="L32" t="s">
+        <v>130</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" t="s">
+        <v>86</v>
+      </c>
+      <c r="E33" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33">
+        <v>51.96</v>
+      </c>
+      <c r="G33" t="s">
+        <v>101</v>
+      </c>
+      <c r="H33">
+        <v>1.69</v>
+      </c>
+      <c r="I33" s="1">
+        <v>87.81</v>
+      </c>
+      <c r="J33">
+        <v>1.79</v>
+      </c>
+      <c r="K33" s="1">
+        <v>93.01000000000001</v>
+      </c>
+      <c r="L33" t="s">
+        <v>131</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34">
+        <v>23.42</v>
+      </c>
+      <c r="G34" t="s">
+        <v>101</v>
+      </c>
+      <c r="H34">
+        <v>1.69</v>
+      </c>
+      <c r="I34" s="1">
+        <v>39.58</v>
+      </c>
+      <c r="J34">
+        <v>1.8</v>
+      </c>
+      <c r="K34" s="1">
+        <v>42.16</v>
+      </c>
+      <c r="L34" t="s">
+        <v>132</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35">
+        <v>56.71</v>
+      </c>
+      <c r="G35" t="s">
+        <v>101</v>
+      </c>
+      <c r="H35">
+        <v>1.69</v>
+      </c>
+      <c r="I35" s="1">
+        <v>95.84</v>
+      </c>
+      <c r="J35">
+        <v>1.94</v>
+      </c>
+      <c r="K35" s="1">
+        <v>110.02</v>
+      </c>
+      <c r="L35" t="s">
+        <v>133</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" t="s">
+        <v>88</v>
+      </c>
+      <c r="E36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36">
+        <v>32.91</v>
+      </c>
+      <c r="G36" t="s">
+        <v>101</v>
+      </c>
+      <c r="H36">
+        <v>1.42</v>
+      </c>
+      <c r="I36" s="1">
+        <v>46.73</v>
+      </c>
+      <c r="J36">
+        <v>1.54</v>
+      </c>
+      <c r="K36" s="1">
+        <v>50.68</v>
+      </c>
+      <c r="L36" t="s">
+        <v>134</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" t="s">
         <v>93</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="E37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37">
+        <v>24.64</v>
+      </c>
+      <c r="G37" t="s">
+        <v>101</v>
+      </c>
+      <c r="H37">
+        <v>1.43</v>
+      </c>
+      <c r="I37" s="1">
+        <v>35.24</v>
+      </c>
+      <c r="J37">
+        <v>1.55</v>
+      </c>
+      <c r="K37" s="1">
+        <v>38.19</v>
+      </c>
+      <c r="L37" t="s">
+        <v>135</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" t="s">
+        <v>87</v>
+      </c>
+      <c r="E38" t="s">
+        <v>95</v>
+      </c>
+      <c r="F38">
+        <v>35.78</v>
+      </c>
+      <c r="G38" t="s">
+        <v>101</v>
+      </c>
+      <c r="H38">
+        <v>1.43</v>
+      </c>
+      <c r="I38" s="1">
+        <v>51.17</v>
+      </c>
+      <c r="J38">
+        <v>1.53</v>
+      </c>
+      <c r="K38" s="1">
+        <v>54.74</v>
+      </c>
+      <c r="L38" t="s">
+        <v>136</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" t="s">
         <v>94</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="E39" t="s">
+        <v>98</v>
+      </c>
+      <c r="F39">
+        <v>30.36</v>
+      </c>
+      <c r="G39" t="s">
+        <v>101</v>
+      </c>
+      <c r="H39">
+        <v>1.71</v>
+      </c>
+      <c r="I39" s="1">
+        <v>51.92</v>
+      </c>
+      <c r="J39">
+        <v>1.82</v>
+      </c>
+      <c r="K39" s="1">
+        <v>55.26</v>
+      </c>
+      <c r="L39" t="s">
+        <v>137</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" t="s">
+        <v>85</v>
+      </c>
+      <c r="E40" t="s">
+        <v>97</v>
+      </c>
+      <c r="F40">
+        <v>23.62</v>
+      </c>
+      <c r="G40" t="s">
+        <v>101</v>
+      </c>
+      <c r="H40">
+        <v>1.65</v>
+      </c>
+      <c r="I40" s="1">
+        <v>38.97</v>
+      </c>
+      <c r="J40">
+        <v>1.71</v>
+      </c>
+      <c r="K40" s="1">
+        <v>40.39</v>
+      </c>
+      <c r="L40" t="s">
+        <v>138</v>
+      </c>
+      <c r="M40">
+        <v>142450</v>
+      </c>
+      <c r="N40" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" t="s">
+        <v>86</v>
+      </c>
+      <c r="E41" t="s">
+        <v>98</v>
+      </c>
+      <c r="F41">
+        <v>45.57</v>
+      </c>
+      <c r="G41" t="s">
+        <v>101</v>
+      </c>
+      <c r="H41">
+        <v>1.71</v>
+      </c>
+      <c r="I41" s="1">
+        <v>77.92</v>
+      </c>
+      <c r="J41">
+        <v>1.83</v>
+      </c>
+      <c r="K41" s="1">
+        <v>83.39</v>
+      </c>
+      <c r="L41" t="s">
+        <v>139</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="F42">
+        <v>19.47</v>
+      </c>
+      <c r="G42" t="s">
+        <v>101</v>
+      </c>
+      <c r="H42">
+        <v>1.43</v>
+      </c>
+      <c r="I42" s="1">
+        <v>27.84</v>
+      </c>
+      <c r="J42">
+        <v>1.54</v>
+      </c>
+      <c r="K42" s="1">
+        <v>29.98</v>
+      </c>
+      <c r="L42" t="s">
+        <v>140</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" t="s">
+        <v>92</v>
+      </c>
+      <c r="E43" t="s">
         <v>96</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="6">
-        <v>349.37</v>
-      </c>
-      <c r="C32" s="6">
+      <c r="F43">
+        <v>55.97</v>
+      </c>
+      <c r="G43" t="s">
+        <v>101</v>
+      </c>
+      <c r="H43">
+        <v>1.73</v>
+      </c>
+      <c r="I43" s="1">
+        <v>96.83</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43" s="1">
+        <v>111.94</v>
+      </c>
+      <c r="L43" t="s">
+        <v>141</v>
+      </c>
+      <c r="M43">
+        <v>500</v>
+      </c>
+      <c r="N43" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44" t="s">
+        <v>69</v>
+      </c>
+      <c r="D44" t="s">
+        <v>83</v>
+      </c>
+      <c r="E44" t="s">
+        <v>96</v>
+      </c>
+      <c r="F44">
+        <v>19.26</v>
+      </c>
+      <c r="G44" t="s">
+        <v>101</v>
+      </c>
+      <c r="H44">
+        <v>1.73</v>
+      </c>
+      <c r="I44" s="1">
+        <v>33.32</v>
+      </c>
+      <c r="J44">
+        <v>2.02</v>
+      </c>
+      <c r="K44" s="1">
+        <v>38.91</v>
+      </c>
+      <c r="L44" t="s">
+        <v>142</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" t="s">
+        <v>81</v>
+      </c>
+      <c r="E45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F45">
+        <v>36.17</v>
+      </c>
+      <c r="G45" t="s">
+        <v>101</v>
+      </c>
+      <c r="H45">
+        <v>1.43</v>
+      </c>
+      <c r="I45" s="1">
+        <v>51.72</v>
+      </c>
+      <c r="J45">
+        <v>1.56</v>
+      </c>
+      <c r="K45" s="1">
+        <v>56.43</v>
+      </c>
+      <c r="L45" t="s">
+        <v>143</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" t="s">
+        <v>80</v>
+      </c>
+      <c r="D46" t="s">
+        <v>94</v>
+      </c>
+      <c r="E46" t="s">
+        <v>95</v>
+      </c>
+      <c r="F46">
+        <v>65.7</v>
+      </c>
+      <c r="G46" t="s">
+        <v>101</v>
+      </c>
+      <c r="H46">
+        <v>1.43</v>
+      </c>
+      <c r="I46" s="1">
+        <v>93.95</v>
+      </c>
+      <c r="J46">
+        <v>1.56</v>
+      </c>
+      <c r="K46" s="1">
+        <v>102.49</v>
+      </c>
+      <c r="L46" t="s">
+        <v>144</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" t="s">
+        <v>96</v>
+      </c>
+      <c r="F47">
+        <v>51.33</v>
+      </c>
+      <c r="G47" t="s">
+        <v>101</v>
+      </c>
+      <c r="H47">
+        <v>1.78</v>
+      </c>
+      <c r="I47" s="1">
+        <v>91.37</v>
+      </c>
+      <c r="J47">
+        <v>2</v>
+      </c>
+      <c r="K47" s="1">
+        <v>102.66</v>
+      </c>
+      <c r="L47" t="s">
+        <v>145</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" t="s">
+        <v>89</v>
+      </c>
+      <c r="E48" t="s">
+        <v>96</v>
+      </c>
+      <c r="F48">
+        <v>56</v>
+      </c>
+      <c r="G48" t="s">
+        <v>101</v>
+      </c>
+      <c r="H48">
+        <v>1.8</v>
+      </c>
+      <c r="I48" s="1">
+        <v>100.8</v>
+      </c>
+      <c r="J48">
+        <v>2</v>
+      </c>
+      <c r="K48" s="1">
+        <v>112</v>
+      </c>
+      <c r="L48" t="s">
+        <v>146</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49" t="s">
+        <v>75</v>
+      </c>
+      <c r="D49" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" t="s">
+        <v>100</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" t="s">
+        <v>102</v>
+      </c>
+      <c r="H49">
+        <v>4.49</v>
+      </c>
+      <c r="I49" s="1">
+        <v>4.49</v>
+      </c>
+      <c r="J49">
+        <v>4.49</v>
+      </c>
+      <c r="K49" s="1">
+        <v>4.49</v>
+      </c>
+      <c r="L49" t="s">
+        <v>146</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" t="s">
+        <v>85</v>
+      </c>
+      <c r="E50" t="s">
+        <v>97</v>
+      </c>
+      <c r="F50">
+        <v>41.96</v>
+      </c>
+      <c r="G50" t="s">
+        <v>101</v>
+      </c>
+      <c r="H50">
+        <v>1.7</v>
+      </c>
+      <c r="I50" s="1">
+        <v>71.33</v>
+      </c>
+      <c r="J50">
+        <v>1.75</v>
+      </c>
+      <c r="K50" s="1">
+        <v>73.43000000000001</v>
+      </c>
+      <c r="L50" t="s">
+        <v>147</v>
+      </c>
+      <c r="M50">
+        <v>142800</v>
+      </c>
+      <c r="N50" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" t="s">
+        <v>76</v>
+      </c>
+      <c r="D51" t="s">
+        <v>90</v>
+      </c>
+      <c r="E51" t="s">
+        <v>98</v>
+      </c>
+      <c r="F51">
+        <v>32.08</v>
+      </c>
+      <c r="G51" t="s">
+        <v>101</v>
+      </c>
+      <c r="H51">
+        <v>1.74</v>
+      </c>
+      <c r="I51" s="1">
+        <v>55.82</v>
+      </c>
+      <c r="J51">
+        <v>1.81</v>
+      </c>
+      <c r="K51" s="1">
+        <v>58.06</v>
+      </c>
+      <c r="L51" t="s">
+        <v>148</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" t="s">
+        <v>81</v>
+      </c>
+      <c r="E52" t="s">
+        <v>95</v>
+      </c>
+      <c r="F52">
+        <v>19.51</v>
+      </c>
+      <c r="G52" t="s">
+        <v>101</v>
+      </c>
+      <c r="H52">
+        <v>1.49</v>
+      </c>
+      <c r="I52" s="1">
+        <v>29.07</v>
+      </c>
+      <c r="J52">
+        <v>1.55</v>
+      </c>
+      <c r="K52" s="1">
+        <v>30.24</v>
+      </c>
+      <c r="L52" t="s">
+        <v>149</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" t="s">
+        <v>66</v>
+      </c>
+      <c r="C53" t="s">
+        <v>69</v>
+      </c>
+      <c r="D53" t="s">
+        <v>83</v>
+      </c>
+      <c r="E53" t="s">
+        <v>97</v>
+      </c>
+      <c r="F53">
+        <v>45.83</v>
+      </c>
+      <c r="G53" t="s">
+        <v>101</v>
+      </c>
+      <c r="H53">
+        <v>1.72</v>
+      </c>
+      <c r="I53" s="1">
+        <v>78.83</v>
+      </c>
+      <c r="J53">
+        <v>1.77</v>
+      </c>
+      <c r="K53" s="1">
+        <v>81.12</v>
+      </c>
+      <c r="L53" t="s">
+        <v>150</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E57" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="7">
-        <v>1.6862</v>
-      </c>
-      <c r="E32" s="6">
-        <v>589.11</v>
-      </c>
-      <c r="F32" s="6">
-        <v>630.1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B33" s="6">
-        <v>253.01</v>
-      </c>
-      <c r="C33" s="6">
-        <v>9</v>
-      </c>
-      <c r="D33" s="7">
-        <v>1.3915</v>
-      </c>
-      <c r="E33" s="6">
-        <v>352.06</v>
-      </c>
-      <c r="F33" s="6">
-        <v>380.17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="6">
-        <v>144.42</v>
-      </c>
-      <c r="C34" s="6">
-        <v>3</v>
-      </c>
-      <c r="D34" s="7">
-        <v>1.6974</v>
-      </c>
-      <c r="E34" s="6">
-        <v>245.14</v>
-      </c>
-      <c r="F34" s="6">
-        <v>254.18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="6">
-        <v>92.86</v>
-      </c>
-      <c r="C35" s="6">
-        <v>3</v>
-      </c>
-      <c r="D35" s="7">
-        <v>1.4357</v>
-      </c>
-      <c r="E35" s="6">
-        <v>133.32</v>
-      </c>
-      <c r="F35" s="6">
-        <v>140.75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="6">
+      <c r="F57" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B58" s="6">
+        <v>647.39</v>
+      </c>
+      <c r="C58" s="6">
+        <v>15</v>
+      </c>
+      <c r="D58" s="7">
+        <v>1.7088</v>
+      </c>
+      <c r="E58" s="6">
+        <v>1106.28</v>
+      </c>
+      <c r="F58" s="6">
+        <v>1217.61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B59" s="6">
+        <v>507.93</v>
+      </c>
+      <c r="C59" s="6">
+        <v>17</v>
+      </c>
+      <c r="D59" s="7">
+        <v>1.4113</v>
+      </c>
+      <c r="E59" s="6">
+        <v>716.8200000000001</v>
+      </c>
+      <c r="F59" s="6">
+        <v>774.03</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B60" s="6">
+        <v>423.25</v>
+      </c>
+      <c r="C60" s="6">
+        <v>10</v>
+      </c>
+      <c r="D60" s="7">
+        <v>1.6999</v>
+      </c>
+      <c r="E60" s="6">
+        <v>719.48</v>
+      </c>
+      <c r="F60" s="6">
+        <v>755.3099999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B61" s="6">
+        <v>204.27</v>
+      </c>
+      <c r="C61" s="6">
+        <v>6</v>
+      </c>
+      <c r="D61" s="7">
+        <v>1.5785</v>
+      </c>
+      <c r="E61" s="6">
+        <v>322.45</v>
+      </c>
+      <c r="F61" s="6">
+        <v>335.69</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B62" s="6">
         <v>2</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C62" s="6">
         <v>2</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D62" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="E62" s="6">
+        <v>8.98</v>
+      </c>
+      <c r="F62" s="6">
+        <v>8.98</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B63" s="6">
+        <v>2</v>
+      </c>
+      <c r="C63" s="6">
+        <v>2</v>
+      </c>
+      <c r="D63" s="7">
         <v>26.83</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E63" s="6">
         <v>53.66</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F63" s="6">
         <v>53.66</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B37" s="6">
-        <v>1</v>
-      </c>
-      <c r="C37" s="6">
-        <v>1</v>
-      </c>
-      <c r="D37" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="E37" s="6">
-        <v>4.49</v>
-      </c>
-      <c r="F37" s="6">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B38" s="9">
-        <v>842.66</v>
-      </c>
-      <c r="C38" s="9">
-        <v>26</v>
-      </c>
-      <c r="D38" s="7"/>
-      <c r="E38" s="9">
-        <v>1377.78</v>
-      </c>
-      <c r="F38" s="9">
-        <v>1463.35</v>
+    <row r="64" spans="1:14">
+      <c r="A64" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B64" s="9">
+        <v>1786.84</v>
+      </c>
+      <c r="C64" s="9">
+        <v>52</v>
+      </c>
+      <c r="D64" s="7"/>
+      <c r="E64" s="9">
+        <v>2927.67</v>
+      </c>
+      <c r="F64" s="9">
+        <v>3145.28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A56:F56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 2/ДЕМАКС АД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 2/ДЕМАКС АД % ГРУПА 2.xlsx
@@ -637,7 +637,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -3420,7 +3420,7 @@
         <v>15</v>
       </c>
       <c r="D58" s="7">
-        <v>1.7088</v>
+        <v>1.708831</v>
       </c>
       <c r="E58" s="6">
         <v>1106.28</v>
@@ -3440,7 +3440,7 @@
         <v>17</v>
       </c>
       <c r="D59" s="7">
-        <v>1.4113</v>
+        <v>1.411257</v>
       </c>
       <c r="E59" s="6">
         <v>716.8200000000001</v>
@@ -3460,7 +3460,7 @@
         <v>10</v>
       </c>
       <c r="D60" s="7">
-        <v>1.6999</v>
+        <v>1.699894</v>
       </c>
       <c r="E60" s="6">
         <v>719.48</v>
@@ -3480,7 +3480,7 @@
         <v>6</v>
       </c>
       <c r="D61" s="7">
-        <v>1.5785</v>
+        <v>1.578548</v>
       </c>
       <c r="E61" s="6">
         <v>322.45</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 2/ДЕМАКС АД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 2/ДЕМАКС АД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="206">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -1028,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1041,13 +1044,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1090,556 +1093,595 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F2">
-        <v>29.95</v>
+        <v>29.947</v>
       </c>
       <c r="G2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H2">
-        <v>1.39</v>
+        <v>1.359</v>
       </c>
       <c r="I2" s="1">
-        <v>41.63</v>
+        <v>1.389</v>
       </c>
       <c r="J2">
+        <v>41.596383</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.52</v>
       </c>
-      <c r="K2" s="1">
-        <v>45.52</v>
-      </c>
-      <c r="L2" t="s">
-        <v>103</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="L2" s="1">
+        <v>45.51944</v>
+      </c>
+      <c r="M2" t="s">
+        <v>104</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F3">
         <v>18.22</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H3">
-        <v>1.39</v>
+        <v>1.359</v>
       </c>
       <c r="I3" s="1">
-        <v>25.33</v>
+        <v>1.389</v>
       </c>
       <c r="J3">
+        <v>25.30758</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.5</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>27.33</v>
       </c>
-      <c r="L3" t="s">
-        <v>104</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="M3" t="s">
+        <v>105</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4">
+        <v>41.712</v>
+      </c>
+      <c r="G4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4">
+        <v>1.619</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.699</v>
+      </c>
+      <c r="J4">
+        <v>70.86868800000001</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="L4" s="1">
+        <v>73.83024</v>
+      </c>
+      <c r="M4" t="s">
+        <v>106</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5">
+        <v>43.861</v>
+      </c>
+      <c r="G5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5">
+        <v>1.619</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.699</v>
+      </c>
+      <c r="J5">
+        <v>74.519839</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="L5" s="1">
+        <v>78.9498</v>
+      </c>
+      <c r="M5" t="s">
+        <v>107</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" t="s">
         <v>96</v>
-      </c>
-      <c r="F4">
-        <v>41.71</v>
-      </c>
-      <c r="G4" t="s">
-        <v>101</v>
-      </c>
-      <c r="H4">
-        <v>1.7</v>
-      </c>
-      <c r="I4" s="1">
-        <v>70.91</v>
-      </c>
-      <c r="J4">
-        <v>1.77</v>
-      </c>
-      <c r="K4" s="1">
-        <v>73.83</v>
-      </c>
-      <c r="L4" t="s">
-        <v>105</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F5">
-        <v>43.86</v>
-      </c>
-      <c r="G5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H5">
-        <v>1.7</v>
-      </c>
-      <c r="I5" s="1">
-        <v>74.56</v>
-      </c>
-      <c r="J5">
-        <v>1.8</v>
-      </c>
-      <c r="K5" s="1">
-        <v>78.95</v>
-      </c>
-      <c r="L5" t="s">
-        <v>106</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" t="s">
-        <v>95</v>
       </c>
       <c r="F6">
         <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H6">
-        <v>1.39</v>
+        <v>1.359</v>
       </c>
       <c r="I6" s="1">
-        <v>37.53</v>
+        <v>1.389</v>
       </c>
       <c r="J6">
+        <v>37.503</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.5</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>40.5</v>
       </c>
-      <c r="L6" t="s">
-        <v>107</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="M6" t="s">
+        <v>108</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F7">
         <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H7">
-        <v>1.43</v>
+        <v>1.399</v>
       </c>
       <c r="I7" s="1">
-        <v>57.2</v>
+        <v>1.429</v>
       </c>
       <c r="J7">
+        <v>57.16</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.51</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>60.4</v>
       </c>
-      <c r="L7" t="s">
-        <v>108</v>
-      </c>
-      <c r="M7">
+      <c r="M7" t="s">
+        <v>109</v>
+      </c>
+      <c r="N7">
         <v>141141</v>
       </c>
-      <c r="N7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F8">
         <v>23.13</v>
       </c>
       <c r="G8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H8">
-        <v>1.7</v>
+        <v>1.619</v>
       </c>
       <c r="I8" s="1">
-        <v>39.32</v>
+        <v>1.699</v>
       </c>
       <c r="J8">
+        <v>39.29787</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.77</v>
       </c>
-      <c r="K8" s="1">
-        <v>40.94</v>
-      </c>
-      <c r="L8" t="s">
-        <v>109</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="L8" s="1">
+        <v>40.9401</v>
+      </c>
+      <c r="M8" t="s">
+        <v>110</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F9">
-        <v>53.35</v>
+        <v>53.352</v>
       </c>
       <c r="G9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H9">
-        <v>1.71</v>
+        <v>1.649</v>
       </c>
       <c r="I9" s="1">
-        <v>91.23</v>
+        <v>1.709</v>
       </c>
       <c r="J9">
+        <v>91.178568</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.76</v>
       </c>
-      <c r="K9" s="1">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="L9" t="s">
-        <v>110</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="L9" s="1">
+        <v>93.89952</v>
+      </c>
+      <c r="M9" t="s">
+        <v>111</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10">
+        <v>42.027</v>
+      </c>
+      <c r="G10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10">
+        <v>1.599</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.679</v>
+      </c>
+      <c r="J10">
+        <v>70.563333</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.82</v>
+      </c>
+      <c r="L10" s="1">
+        <v>76.48914000000001</v>
+      </c>
+      <c r="M10" t="s">
+        <v>112</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" t="s">
         <v>96</v>
-      </c>
-      <c r="F10">
-        <v>42.03</v>
-      </c>
-      <c r="G10" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10">
-        <v>1.68</v>
-      </c>
-      <c r="I10" s="1">
-        <v>70.61</v>
-      </c>
-      <c r="J10">
-        <v>1.82</v>
-      </c>
-      <c r="K10" s="1">
-        <v>76.48999999999999</v>
-      </c>
-      <c r="L10" t="s">
-        <v>111</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" t="s">
-        <v>95</v>
       </c>
       <c r="F11">
         <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H11">
-        <v>1.39</v>
+        <v>1.359</v>
       </c>
       <c r="I11" s="1">
-        <v>38.92</v>
+        <v>1.389</v>
       </c>
       <c r="J11">
+        <v>38.892</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.49</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>41.72</v>
       </c>
-      <c r="L11" t="s">
-        <v>112</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="M11" t="s">
+        <v>113</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F12">
-        <v>22.68</v>
+        <v>22.682</v>
       </c>
       <c r="G12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H12">
-        <v>1.39</v>
+        <v>1.359</v>
       </c>
       <c r="I12" s="1">
-        <v>31.53</v>
+        <v>1.389</v>
       </c>
       <c r="J12">
+        <v>31.505298</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.51</v>
       </c>
-      <c r="K12" s="1">
-        <v>34.25</v>
-      </c>
-      <c r="L12" t="s">
-        <v>113</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="L12" s="1">
+        <v>34.24982</v>
+      </c>
+      <c r="M12" t="s">
+        <v>114</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F13">
-        <v>27.82</v>
+        <v>27.822</v>
       </c>
       <c r="G13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H13">
-        <v>1.44</v>
+        <v>1.406</v>
       </c>
       <c r="I13" s="1">
-        <v>40.06</v>
+        <v>1.436</v>
       </c>
       <c r="J13">
+        <v>39.952392</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.52</v>
       </c>
-      <c r="K13" s="1">
-        <v>42.29</v>
-      </c>
-      <c r="L13" t="s">
-        <v>114</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="L13" s="1">
+        <v>42.28944</v>
+      </c>
+      <c r="M13" t="s">
+        <v>115</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H14">
         <v>26.83</v>
@@ -1653,81 +1695,87 @@
       <c r="K14" s="1">
         <v>26.83</v>
       </c>
-      <c r="L14" t="s">
-        <v>114</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="L14" s="1">
+        <v>26.83</v>
+      </c>
+      <c r="M14" t="s">
+        <v>115</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F15">
-        <v>25.04</v>
+        <v>25.039</v>
       </c>
       <c r="G15" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15">
+        <v>1.406</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1.436</v>
+      </c>
+      <c r="J15">
+        <v>35.956004</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L15" s="1">
+        <v>38.05928</v>
+      </c>
+      <c r="M15" t="s">
+        <v>116</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" t="s">
         <v>101</v>
-      </c>
-      <c r="H15">
-        <v>1.44</v>
-      </c>
-      <c r="I15" s="1">
-        <v>36.06</v>
-      </c>
-      <c r="J15">
-        <v>1.52</v>
-      </c>
-      <c r="K15" s="1">
-        <v>38.06</v>
-      </c>
-      <c r="L15" t="s">
-        <v>115</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" t="s">
-        <v>89</v>
-      </c>
-      <c r="E16" t="s">
-        <v>100</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H16">
         <v>4.49</v>
@@ -1741,169 +1789,181 @@
       <c r="K16" s="1">
         <v>4.49</v>
       </c>
-      <c r="L16" t="s">
-        <v>115</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="L16" s="1">
+        <v>4.49</v>
+      </c>
+      <c r="M16" t="s">
+        <v>116</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F17">
-        <v>40.98</v>
+        <v>40.977</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H17">
-        <v>1.69</v>
+        <v>1.629</v>
       </c>
       <c r="I17" s="1">
-        <v>69.26000000000001</v>
+        <v>1.689</v>
       </c>
       <c r="J17">
+        <v>69.21015300000001</v>
+      </c>
+      <c r="K17" s="1">
         <v>1.76</v>
       </c>
-      <c r="K17" s="1">
-        <v>72.12</v>
-      </c>
-      <c r="L17" t="s">
-        <v>116</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="L17" s="1">
+        <v>72.11951999999999</v>
+      </c>
+      <c r="M17" t="s">
+        <v>117</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F18">
-        <v>26.29</v>
+        <v>26.293</v>
       </c>
       <c r="G18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H18">
-        <v>1.39</v>
+        <v>1.359</v>
       </c>
       <c r="I18" s="1">
-        <v>36.54</v>
+        <v>1.389</v>
       </c>
       <c r="J18">
+        <v>36.520977</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.5</v>
       </c>
-      <c r="K18" s="1">
-        <v>39.44</v>
-      </c>
-      <c r="L18" t="s">
-        <v>117</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="L18" s="1">
+        <v>39.4395</v>
+      </c>
+      <c r="M18" t="s">
+        <v>118</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F19">
         <v>35</v>
       </c>
       <c r="G19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H19">
-        <v>1.68</v>
+        <v>1.599</v>
       </c>
       <c r="I19" s="1">
-        <v>58.8</v>
+        <v>1.679</v>
       </c>
       <c r="J19">
+        <v>58.765</v>
+      </c>
+      <c r="K19" s="1">
         <v>1.78</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>62.3</v>
       </c>
-      <c r="L19" t="s">
-        <v>118</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="M19" t="s">
+        <v>119</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H20">
         <v>26.83</v>
@@ -1917,1269 +1977,1356 @@
       <c r="K20" s="1">
         <v>26.83</v>
       </c>
-      <c r="L20" t="s">
-        <v>118</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="L20" s="1">
+        <v>26.83</v>
+      </c>
+      <c r="M20" t="s">
+        <v>119</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F21">
         <v>35.56</v>
       </c>
       <c r="G21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H21">
-        <v>1.39</v>
+        <v>1.359</v>
       </c>
       <c r="I21" s="1">
-        <v>49.43</v>
+        <v>1.389</v>
       </c>
       <c r="J21">
+        <v>49.39284</v>
+      </c>
+      <c r="K21" s="1">
         <v>1.5</v>
       </c>
-      <c r="K21" s="1">
+      <c r="L21" s="1">
         <v>53.34</v>
       </c>
-      <c r="L21" t="s">
-        <v>119</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="M21" t="s">
+        <v>120</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22">
+        <v>64.02800000000001</v>
+      </c>
+      <c r="G22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H22">
+        <v>1.599</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1.679</v>
+      </c>
+      <c r="J22">
+        <v>107.503012</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="L22" s="1">
+        <v>115.2504</v>
+      </c>
+      <c r="M22" t="s">
+        <v>121</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23">
+        <v>50.091</v>
+      </c>
+      <c r="G23" t="s">
+        <v>102</v>
+      </c>
+      <c r="H23">
+        <v>1.629</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1.689</v>
+      </c>
+      <c r="J23">
+        <v>84.60369900000001</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="L23" s="1">
+        <v>88.16016</v>
+      </c>
+      <c r="M23" t="s">
+        <v>122</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" t="s">
         <v>96</v>
-      </c>
-      <c r="F22">
-        <v>64.03</v>
-      </c>
-      <c r="G22" t="s">
-        <v>101</v>
-      </c>
-      <c r="H22">
-        <v>1.68</v>
-      </c>
-      <c r="I22" s="1">
-        <v>107.57</v>
-      </c>
-      <c r="J22">
-        <v>1.8</v>
-      </c>
-      <c r="K22" s="1">
-        <v>115.25</v>
-      </c>
-      <c r="L22" t="s">
-        <v>120</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" t="s">
-        <v>86</v>
-      </c>
-      <c r="E23" t="s">
-        <v>98</v>
-      </c>
-      <c r="F23">
-        <v>50.09</v>
-      </c>
-      <c r="G23" t="s">
-        <v>101</v>
-      </c>
-      <c r="H23">
-        <v>1.69</v>
-      </c>
-      <c r="I23" s="1">
-        <v>84.65000000000001</v>
-      </c>
-      <c r="J23">
-        <v>1.76</v>
-      </c>
-      <c r="K23" s="1">
-        <v>88.16</v>
-      </c>
-      <c r="L23" t="s">
-        <v>121</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" t="s">
-        <v>95</v>
       </c>
       <c r="F24">
         <v>27.55</v>
       </c>
       <c r="G24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H24">
-        <v>1.39</v>
+        <v>1.359</v>
       </c>
       <c r="I24" s="1">
-        <v>38.29</v>
+        <v>1.389</v>
       </c>
       <c r="J24">
+        <v>38.26695</v>
+      </c>
+      <c r="K24" s="1">
         <v>1.49</v>
       </c>
-      <c r="K24" s="1">
-        <v>41.05</v>
-      </c>
-      <c r="L24" t="s">
-        <v>122</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="L24" s="1">
+        <v>41.0495</v>
+      </c>
+      <c r="M24" t="s">
+        <v>123</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F25">
-        <v>46.99</v>
+        <v>46.989</v>
       </c>
       <c r="G25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H25">
-        <v>1.68</v>
+        <v>1.599</v>
       </c>
       <c r="I25" s="1">
-        <v>78.94</v>
+        <v>1.679</v>
       </c>
       <c r="J25">
+        <v>78.894531</v>
+      </c>
+      <c r="K25" s="1">
         <v>1.82</v>
       </c>
-      <c r="K25" s="1">
-        <v>85.52</v>
-      </c>
-      <c r="L25" t="s">
-        <v>123</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="L25" s="1">
+        <v>85.51998</v>
+      </c>
+      <c r="M25" t="s">
+        <v>124</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F26">
         <v>52.62</v>
       </c>
       <c r="G26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H26">
-        <v>1.68</v>
+        <v>1.599</v>
       </c>
       <c r="I26" s="1">
-        <v>88.40000000000001</v>
+        <v>1.679</v>
       </c>
       <c r="J26">
+        <v>88.34898</v>
+      </c>
+      <c r="K26" s="1">
         <v>1.84</v>
       </c>
-      <c r="K26" s="1">
-        <v>96.81999999999999</v>
-      </c>
-      <c r="L26" t="s">
-        <v>124</v>
-      </c>
-      <c r="M26">
+      <c r="L26" s="1">
+        <v>96.82080000000001</v>
+      </c>
+      <c r="M26" t="s">
+        <v>125</v>
+      </c>
+      <c r="N26">
         <v>142000</v>
       </c>
-      <c r="N26" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F27">
-        <v>37.76</v>
+        <v>37.762</v>
       </c>
       <c r="G27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H27">
-        <v>1.4</v>
+        <v>1.369</v>
       </c>
       <c r="I27" s="1">
-        <v>52.86</v>
+        <v>1.399</v>
       </c>
       <c r="J27">
+        <v>52.829038</v>
+      </c>
+      <c r="K27" s="1">
         <v>1.51</v>
       </c>
-      <c r="K27" s="1">
-        <v>57.02</v>
-      </c>
-      <c r="L27" t="s">
-        <v>125</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="L27" s="1">
+        <v>57.02062</v>
+      </c>
+      <c r="M27" t="s">
+        <v>126</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F28">
         <v>20.74</v>
       </c>
       <c r="G28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H28">
-        <v>1.4</v>
+        <v>1.369</v>
       </c>
       <c r="I28" s="1">
-        <v>29.04</v>
+        <v>1.399</v>
       </c>
       <c r="J28">
+        <v>29.01526</v>
+      </c>
+      <c r="K28" s="1">
         <v>1.5</v>
       </c>
-      <c r="K28" s="1">
+      <c r="L28" s="1">
         <v>31.11</v>
       </c>
-      <c r="L28" t="s">
-        <v>126</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="M28" t="s">
+        <v>127</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F29">
-        <v>32.02</v>
+        <v>32.022</v>
       </c>
       <c r="G29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H29">
-        <v>1.69</v>
+        <v>1.629</v>
       </c>
       <c r="I29" s="1">
-        <v>54.11</v>
+        <v>1.689</v>
       </c>
       <c r="J29">
+        <v>54.085158</v>
+      </c>
+      <c r="K29" s="1">
         <v>1.78</v>
       </c>
-      <c r="K29" s="1">
-        <v>57</v>
-      </c>
-      <c r="L29" t="s">
-        <v>127</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="L29" s="1">
+        <v>56.99916</v>
+      </c>
+      <c r="M29" t="s">
+        <v>128</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F30">
         <v>27.18</v>
       </c>
       <c r="G30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H30">
-        <v>1.68</v>
+        <v>1.599</v>
       </c>
       <c r="I30" s="1">
-        <v>45.66</v>
+        <v>1.679</v>
       </c>
       <c r="J30">
+        <v>45.63522</v>
+      </c>
+      <c r="K30" s="1">
         <v>1.89</v>
       </c>
-      <c r="K30" s="1">
-        <v>51.37</v>
-      </c>
-      <c r="L30" t="s">
-        <v>128</v>
-      </c>
-      <c r="M30">
+      <c r="L30" s="1">
+        <v>51.3702</v>
+      </c>
+      <c r="M30" t="s">
+        <v>129</v>
+      </c>
+      <c r="N30">
         <v>300</v>
       </c>
-      <c r="N30" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" t="s">
+        <v>99</v>
+      </c>
+      <c r="F31">
+        <v>63.418</v>
+      </c>
+      <c r="G31" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31">
+        <v>1.629</v>
+      </c>
+      <c r="I31" s="1">
+        <v>1.689</v>
+      </c>
+      <c r="J31">
+        <v>107.113002</v>
+      </c>
+      <c r="K31" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="L31" s="1">
+        <v>112.24986</v>
+      </c>
+      <c r="M31" t="s">
+        <v>130</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" t="s">
+        <v>97</v>
+      </c>
+      <c r="F32">
+        <v>31.568</v>
+      </c>
+      <c r="G32" t="s">
+        <v>102</v>
+      </c>
+      <c r="H32">
+        <v>1.608</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1.688</v>
+      </c>
+      <c r="J32">
+        <v>53.286784</v>
+      </c>
+      <c r="K32" s="1">
+        <v>1.92</v>
+      </c>
+      <c r="L32" s="1">
+        <v>60.61056</v>
+      </c>
+      <c r="M32" t="s">
+        <v>131</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" t="s">
+        <v>99</v>
+      </c>
+      <c r="F33">
+        <v>51.961</v>
+      </c>
+      <c r="G33" t="s">
+        <v>102</v>
+      </c>
+      <c r="H33">
+        <v>1.629</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1.689</v>
+      </c>
+      <c r="J33">
+        <v>87.762129</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1.79</v>
+      </c>
+      <c r="L33" s="1">
+        <v>93.01018999999999</v>
+      </c>
+      <c r="M33" t="s">
+        <v>132</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34">
+        <v>23.422</v>
+      </c>
+      <c r="G34" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34">
+        <v>1.629</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1.689</v>
+      </c>
+      <c r="J34">
+        <v>39.559758</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="L34" s="1">
+        <v>42.1596</v>
+      </c>
+      <c r="M34" t="s">
+        <v>133</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" t="s">
+        <v>83</v>
+      </c>
+      <c r="E35" t="s">
+        <v>97</v>
+      </c>
+      <c r="F35">
+        <v>56.711</v>
+      </c>
+      <c r="G35" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35">
+        <v>1.608</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1.688</v>
+      </c>
+      <c r="J35">
+        <v>95.728168</v>
+      </c>
+      <c r="K35" s="1">
+        <v>1.94</v>
+      </c>
+      <c r="L35" s="1">
+        <v>110.01934</v>
+      </c>
+      <c r="M35" t="s">
+        <v>134</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36">
+        <v>32.909</v>
+      </c>
+      <c r="G36" t="s">
+        <v>102</v>
+      </c>
+      <c r="H36">
+        <v>1.389</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1.419</v>
+      </c>
+      <c r="J36">
+        <v>46.697871</v>
+      </c>
+      <c r="K36" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L36" s="1">
+        <v>50.67986</v>
+      </c>
+      <c r="M36" t="s">
+        <v>135</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" t="s">
+        <v>96</v>
+      </c>
+      <c r="F37">
+        <v>24.639</v>
+      </c>
+      <c r="G37" t="s">
+        <v>102</v>
+      </c>
+      <c r="H37">
+        <v>1.401</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1.431</v>
+      </c>
+      <c r="J37">
+        <v>35.258409</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L37" s="1">
+        <v>38.19045</v>
+      </c>
+      <c r="M37" t="s">
+        <v>136</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" t="s">
+        <v>88</v>
+      </c>
+      <c r="E38" t="s">
+        <v>96</v>
+      </c>
+      <c r="F38">
+        <v>35.778</v>
+      </c>
+      <c r="G38" t="s">
+        <v>102</v>
+      </c>
+      <c r="H38">
+        <v>1.401</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1.431</v>
+      </c>
+      <c r="J38">
+        <v>51.198318</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="L38" s="1">
+        <v>54.74034</v>
+      </c>
+      <c r="M38" t="s">
+        <v>137</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" t="s">
+        <v>95</v>
+      </c>
+      <c r="E39" t="s">
+        <v>99</v>
+      </c>
+      <c r="F39">
+        <v>30.363</v>
+      </c>
+      <c r="G39" t="s">
+        <v>102</v>
+      </c>
+      <c r="H39">
+        <v>1.649</v>
+      </c>
+      <c r="I39" s="1">
+        <v>1.709</v>
+      </c>
+      <c r="J39">
+        <v>51.890367</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1.82</v>
+      </c>
+      <c r="L39" s="1">
+        <v>55.26066</v>
+      </c>
+      <c r="M39" t="s">
+        <v>138</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" t="s">
         <v>72</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D40" t="s">
         <v>86</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E40" t="s">
         <v>98</v>
-      </c>
-      <c r="F31">
-        <v>63.42</v>
-      </c>
-      <c r="G31" t="s">
-        <v>101</v>
-      </c>
-      <c r="H31">
-        <v>1.69</v>
-      </c>
-      <c r="I31" s="1">
-        <v>107.18</v>
-      </c>
-      <c r="J31">
-        <v>1.77</v>
-      </c>
-      <c r="K31" s="1">
-        <v>112.25</v>
-      </c>
-      <c r="L31" t="s">
-        <v>129</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" t="s">
-        <v>69</v>
-      </c>
-      <c r="D32" t="s">
-        <v>83</v>
-      </c>
-      <c r="E32" t="s">
-        <v>96</v>
-      </c>
-      <c r="F32">
-        <v>31.57</v>
-      </c>
-      <c r="G32" t="s">
-        <v>101</v>
-      </c>
-      <c r="H32">
-        <v>1.69</v>
-      </c>
-      <c r="I32" s="1">
-        <v>53.35</v>
-      </c>
-      <c r="J32">
-        <v>1.92</v>
-      </c>
-      <c r="K32" s="1">
-        <v>60.61</v>
-      </c>
-      <c r="L32" t="s">
-        <v>130</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" t="s">
-        <v>86</v>
-      </c>
-      <c r="E33" t="s">
-        <v>98</v>
-      </c>
-      <c r="F33">
-        <v>51.96</v>
-      </c>
-      <c r="G33" t="s">
-        <v>101</v>
-      </c>
-      <c r="H33">
-        <v>1.69</v>
-      </c>
-      <c r="I33" s="1">
-        <v>87.81</v>
-      </c>
-      <c r="J33">
-        <v>1.79</v>
-      </c>
-      <c r="K33" s="1">
-        <v>93.01000000000001</v>
-      </c>
-      <c r="L33" t="s">
-        <v>131</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" t="s">
-        <v>72</v>
-      </c>
-      <c r="D34" t="s">
-        <v>86</v>
-      </c>
-      <c r="E34" t="s">
-        <v>98</v>
-      </c>
-      <c r="F34">
-        <v>23.42</v>
-      </c>
-      <c r="G34" t="s">
-        <v>101</v>
-      </c>
-      <c r="H34">
-        <v>1.69</v>
-      </c>
-      <c r="I34" s="1">
-        <v>39.58</v>
-      </c>
-      <c r="J34">
-        <v>1.8</v>
-      </c>
-      <c r="K34" s="1">
-        <v>42.16</v>
-      </c>
-      <c r="L34" t="s">
-        <v>132</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" t="s">
-        <v>68</v>
-      </c>
-      <c r="D35" t="s">
-        <v>82</v>
-      </c>
-      <c r="E35" t="s">
-        <v>96</v>
-      </c>
-      <c r="F35">
-        <v>56.71</v>
-      </c>
-      <c r="G35" t="s">
-        <v>101</v>
-      </c>
-      <c r="H35">
-        <v>1.69</v>
-      </c>
-      <c r="I35" s="1">
-        <v>95.84</v>
-      </c>
-      <c r="J35">
-        <v>1.94</v>
-      </c>
-      <c r="K35" s="1">
-        <v>110.02</v>
-      </c>
-      <c r="L35" t="s">
-        <v>133</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="A36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" t="s">
-        <v>88</v>
-      </c>
-      <c r="E36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F36">
-        <v>32.91</v>
-      </c>
-      <c r="G36" t="s">
-        <v>101</v>
-      </c>
-      <c r="H36">
-        <v>1.42</v>
-      </c>
-      <c r="I36" s="1">
-        <v>46.73</v>
-      </c>
-      <c r="J36">
-        <v>1.54</v>
-      </c>
-      <c r="K36" s="1">
-        <v>50.68</v>
-      </c>
-      <c r="L36" t="s">
-        <v>134</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="A37" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E37" t="s">
-        <v>95</v>
-      </c>
-      <c r="F37">
-        <v>24.64</v>
-      </c>
-      <c r="G37" t="s">
-        <v>101</v>
-      </c>
-      <c r="H37">
-        <v>1.43</v>
-      </c>
-      <c r="I37" s="1">
-        <v>35.24</v>
-      </c>
-      <c r="J37">
-        <v>1.55</v>
-      </c>
-      <c r="K37" s="1">
-        <v>38.19</v>
-      </c>
-      <c r="L37" t="s">
-        <v>135</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" t="s">
-        <v>73</v>
-      </c>
-      <c r="D38" t="s">
-        <v>87</v>
-      </c>
-      <c r="E38" t="s">
-        <v>95</v>
-      </c>
-      <c r="F38">
-        <v>35.78</v>
-      </c>
-      <c r="G38" t="s">
-        <v>101</v>
-      </c>
-      <c r="H38">
-        <v>1.43</v>
-      </c>
-      <c r="I38" s="1">
-        <v>51.17</v>
-      </c>
-      <c r="J38">
-        <v>1.53</v>
-      </c>
-      <c r="K38" s="1">
-        <v>54.74</v>
-      </c>
-      <c r="L38" t="s">
-        <v>136</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" t="s">
-        <v>62</v>
-      </c>
-      <c r="C39" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" t="s">
-        <v>94</v>
-      </c>
-      <c r="E39" t="s">
-        <v>98</v>
-      </c>
-      <c r="F39">
-        <v>30.36</v>
-      </c>
-      <c r="G39" t="s">
-        <v>101</v>
-      </c>
-      <c r="H39">
-        <v>1.71</v>
-      </c>
-      <c r="I39" s="1">
-        <v>51.92</v>
-      </c>
-      <c r="J39">
-        <v>1.82</v>
-      </c>
-      <c r="K39" s="1">
-        <v>55.26</v>
-      </c>
-      <c r="L39" t="s">
-        <v>137</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" t="s">
-        <v>71</v>
-      </c>
-      <c r="D40" t="s">
-        <v>85</v>
-      </c>
-      <c r="E40" t="s">
-        <v>97</v>
       </c>
       <c r="F40">
         <v>23.62</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H40">
-        <v>1.65</v>
+        <v>1.619</v>
       </c>
       <c r="I40" s="1">
-        <v>38.97</v>
+        <v>1.649</v>
       </c>
       <c r="J40">
+        <v>38.94938</v>
+      </c>
+      <c r="K40" s="1">
         <v>1.71</v>
       </c>
-      <c r="K40" s="1">
-        <v>40.39</v>
-      </c>
-      <c r="L40" t="s">
-        <v>138</v>
-      </c>
-      <c r="M40">
+      <c r="L40" s="1">
+        <v>40.3902</v>
+      </c>
+      <c r="M40" t="s">
+        <v>139</v>
+      </c>
+      <c r="N40">
         <v>142450</v>
       </c>
-      <c r="N40" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E41" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F41">
-        <v>45.57</v>
+        <v>45.568</v>
       </c>
       <c r="G41" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H41">
-        <v>1.71</v>
+        <v>1.649</v>
       </c>
       <c r="I41" s="1">
-        <v>77.92</v>
+        <v>1.709</v>
       </c>
       <c r="J41">
+        <v>77.87571199999999</v>
+      </c>
+      <c r="K41" s="1">
         <v>1.83</v>
       </c>
-      <c r="K41" s="1">
-        <v>83.39</v>
-      </c>
-      <c r="L41" t="s">
-        <v>139</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="L41" s="1">
+        <v>83.38943999999999</v>
+      </c>
+      <c r="M41" t="s">
+        <v>140</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C42" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F42">
-        <v>19.47</v>
+        <v>19.468</v>
       </c>
       <c r="G42" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H42">
-        <v>1.43</v>
+        <v>1.401</v>
       </c>
       <c r="I42" s="1">
-        <v>27.84</v>
+        <v>1.431</v>
       </c>
       <c r="J42">
+        <v>27.858708</v>
+      </c>
+      <c r="K42" s="1">
         <v>1.54</v>
       </c>
-      <c r="K42" s="1">
-        <v>29.98</v>
-      </c>
-      <c r="L42" t="s">
-        <v>140</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="L42" s="1">
+        <v>29.98072</v>
+      </c>
+      <c r="M42" t="s">
+        <v>141</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D43" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F43">
         <v>55.97</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H43">
-        <v>1.73</v>
+        <v>1.648</v>
       </c>
       <c r="I43" s="1">
-        <v>96.83</v>
+        <v>1.728</v>
       </c>
       <c r="J43">
+        <v>96.71616</v>
+      </c>
+      <c r="K43" s="1">
         <v>2</v>
       </c>
-      <c r="K43" s="1">
+      <c r="L43" s="1">
         <v>111.94</v>
       </c>
-      <c r="L43" t="s">
-        <v>141</v>
-      </c>
-      <c r="M43">
+      <c r="M43" t="s">
+        <v>142</v>
+      </c>
+      <c r="N43">
         <v>500</v>
       </c>
-      <c r="N43" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C44" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" t="s">
+        <v>97</v>
+      </c>
+      <c r="F44">
+        <v>19.262</v>
+      </c>
+      <c r="G44" t="s">
+        <v>102</v>
+      </c>
+      <c r="H44">
+        <v>1.648</v>
+      </c>
+      <c r="I44" s="1">
+        <v>1.728</v>
+      </c>
+      <c r="J44">
+        <v>33.284736</v>
+      </c>
+      <c r="K44" s="1">
+        <v>2.02</v>
+      </c>
+      <c r="L44" s="1">
+        <v>38.90924</v>
+      </c>
+      <c r="M44" t="s">
+        <v>143</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45" t="s">
+        <v>96</v>
+      </c>
+      <c r="F45">
+        <v>36.173</v>
+      </c>
+      <c r="G45" t="s">
+        <v>102</v>
+      </c>
+      <c r="H45">
+        <v>1.401</v>
+      </c>
+      <c r="I45" s="1">
+        <v>1.431</v>
+      </c>
+      <c r="J45">
+        <v>51.763563</v>
+      </c>
+      <c r="K45" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L45" s="1">
+        <v>56.42988</v>
+      </c>
+      <c r="M45" t="s">
+        <v>144</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" t="s">
+        <v>95</v>
+      </c>
+      <c r="E46" t="s">
+        <v>96</v>
+      </c>
+      <c r="F46">
+        <v>65.699</v>
+      </c>
+      <c r="G46" t="s">
+        <v>102</v>
+      </c>
+      <c r="H46">
+        <v>1.401</v>
+      </c>
+      <c r="I46" s="1">
+        <v>1.431</v>
+      </c>
+      <c r="J46">
+        <v>94.015269</v>
+      </c>
+      <c r="K46" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L46" s="1">
+        <v>102.49044</v>
+      </c>
+      <c r="M46" t="s">
+        <v>145</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" t="s">
         <v>69</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D47" t="s">
         <v>83</v>
       </c>
-      <c r="E44" t="s">
-        <v>96</v>
-      </c>
-      <c r="F44">
-        <v>19.26</v>
-      </c>
-      <c r="G44" t="s">
-        <v>101</v>
-      </c>
-      <c r="H44">
-        <v>1.73</v>
-      </c>
-      <c r="I44" s="1">
-        <v>33.32</v>
-      </c>
-      <c r="J44">
-        <v>2.02</v>
-      </c>
-      <c r="K44" s="1">
-        <v>38.91</v>
-      </c>
-      <c r="L44" t="s">
-        <v>142</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" t="s">
-        <v>36</v>
-      </c>
-      <c r="B45" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" t="s">
-        <v>81</v>
-      </c>
-      <c r="E45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F45">
-        <v>36.17</v>
-      </c>
-      <c r="G45" t="s">
-        <v>101</v>
-      </c>
-      <c r="H45">
-        <v>1.43</v>
-      </c>
-      <c r="I45" s="1">
-        <v>51.72</v>
-      </c>
-      <c r="J45">
-        <v>1.56</v>
-      </c>
-      <c r="K45" s="1">
-        <v>56.43</v>
-      </c>
-      <c r="L45" t="s">
-        <v>143</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" t="s">
-        <v>36</v>
-      </c>
-      <c r="B46" t="s">
-        <v>65</v>
-      </c>
-      <c r="C46" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46" t="s">
-        <v>94</v>
-      </c>
-      <c r="E46" t="s">
-        <v>95</v>
-      </c>
-      <c r="F46">
-        <v>65.7</v>
-      </c>
-      <c r="G46" t="s">
-        <v>101</v>
-      </c>
-      <c r="H46">
-        <v>1.43</v>
-      </c>
-      <c r="I46" s="1">
-        <v>93.95</v>
-      </c>
-      <c r="J46">
-        <v>1.56</v>
-      </c>
-      <c r="K46" s="1">
-        <v>102.49</v>
-      </c>
-      <c r="L46" t="s">
-        <v>144</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" t="s">
-        <v>43</v>
-      </c>
-      <c r="C47" t="s">
-        <v>68</v>
-      </c>
-      <c r="D47" t="s">
-        <v>82</v>
-      </c>
       <c r="E47" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F47">
         <v>51.33</v>
       </c>
       <c r="G47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H47">
-        <v>1.78</v>
+        <v>1.702</v>
       </c>
       <c r="I47" s="1">
-        <v>91.37</v>
+        <v>1.782</v>
       </c>
       <c r="J47">
+        <v>91.47006</v>
+      </c>
+      <c r="K47" s="1">
         <v>2</v>
       </c>
-      <c r="K47" s="1">
+      <c r="L47" s="1">
         <v>102.66</v>
       </c>
-      <c r="L47" t="s">
-        <v>145</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="M47" t="s">
+        <v>146</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C48" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D48" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E48" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F48">
         <v>56</v>
       </c>
       <c r="G48" t="s">
+        <v>102</v>
+      </c>
+      <c r="H48">
+        <v>1.716</v>
+      </c>
+      <c r="I48" s="1">
+        <v>1.796</v>
+      </c>
+      <c r="J48">
+        <v>100.576</v>
+      </c>
+      <c r="K48" s="1">
+        <v>2</v>
+      </c>
+      <c r="L48" s="1">
+        <v>112</v>
+      </c>
+      <c r="M48" t="s">
+        <v>147</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" t="s">
+        <v>76</v>
+      </c>
+      <c r="D49" t="s">
+        <v>90</v>
+      </c>
+      <c r="E49" t="s">
         <v>101</v>
-      </c>
-      <c r="H48">
-        <v>1.8</v>
-      </c>
-      <c r="I48" s="1">
-        <v>100.8</v>
-      </c>
-      <c r="J48">
-        <v>2</v>
-      </c>
-      <c r="K48" s="1">
-        <v>112</v>
-      </c>
-      <c r="L48" t="s">
-        <v>146</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
-      <c r="A49" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" t="s">
-        <v>43</v>
-      </c>
-      <c r="C49" t="s">
-        <v>75</v>
-      </c>
-      <c r="D49" t="s">
-        <v>89</v>
-      </c>
-      <c r="E49" t="s">
-        <v>100</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H49">
         <v>4.49</v>
@@ -3193,195 +3340,210 @@
       <c r="K49" s="1">
         <v>4.49</v>
       </c>
-      <c r="L49" t="s">
-        <v>146</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="L49" s="1">
+        <v>4.49</v>
+      </c>
+      <c r="M49" t="s">
+        <v>147</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D50" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F50">
         <v>41.96</v>
       </c>
       <c r="G50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H50">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I50" s="1">
-        <v>71.33</v>
+        <v>1.704</v>
       </c>
       <c r="J50">
+        <v>71.49984000000001</v>
+      </c>
+      <c r="K50" s="1">
         <v>1.75</v>
       </c>
-      <c r="K50" s="1">
+      <c r="L50" s="1">
         <v>73.43000000000001</v>
       </c>
-      <c r="L50" t="s">
-        <v>147</v>
-      </c>
-      <c r="M50">
+      <c r="M50" t="s">
+        <v>148</v>
+      </c>
+      <c r="N50">
         <v>142800</v>
       </c>
-      <c r="N50" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F51">
-        <v>32.08</v>
+        <v>32.077</v>
       </c>
       <c r="G51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H51">
-        <v>1.74</v>
+        <v>1.676</v>
       </c>
       <c r="I51" s="1">
-        <v>55.82</v>
+        <v>1.736</v>
       </c>
       <c r="J51">
+        <v>55.685672</v>
+      </c>
+      <c r="K51" s="1">
         <v>1.81</v>
       </c>
-      <c r="K51" s="1">
-        <v>58.06</v>
-      </c>
-      <c r="L51" t="s">
-        <v>148</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="L51" s="1">
+        <v>58.05937</v>
+      </c>
+      <c r="M51" t="s">
+        <v>149</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D52" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E52" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F52">
         <v>19.51</v>
       </c>
       <c r="G52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H52">
-        <v>1.49</v>
+        <v>1.459</v>
       </c>
       <c r="I52" s="1">
-        <v>29.07</v>
+        <v>1.489</v>
       </c>
       <c r="J52">
+        <v>29.05039</v>
+      </c>
+      <c r="K52" s="1">
         <v>1.55</v>
       </c>
-      <c r="K52" s="1">
-        <v>30.24</v>
-      </c>
-      <c r="L52" t="s">
-        <v>149</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="L52" s="1">
+        <v>30.2405</v>
+      </c>
+      <c r="M52" t="s">
+        <v>150</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E53" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F53">
-        <v>45.83</v>
+        <v>45.831</v>
       </c>
       <c r="G53" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H53">
-        <v>1.72</v>
+        <v>1.689</v>
       </c>
       <c r="I53" s="1">
-        <v>78.83</v>
+        <v>1.719</v>
       </c>
       <c r="J53">
+        <v>78.783489</v>
+      </c>
+      <c r="K53" s="1">
         <v>1.77</v>
       </c>
-      <c r="K53" s="1">
-        <v>81.12</v>
-      </c>
-      <c r="L53" t="s">
-        <v>150</v>
-      </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
-      <c r="N53" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
+      <c r="L53" s="1">
+        <v>81.12087</v>
+      </c>
+      <c r="M53" t="s">
+        <v>151</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -3389,49 +3551,49 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:15">
       <c r="A57" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
       <c r="A58" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B58" s="6">
-        <v>647.39</v>
+        <v>647.388</v>
       </c>
       <c r="C58" s="6">
         <v>15</v>
       </c>
       <c r="D58" s="7">
-        <v>1.708831</v>
+        <v>1.707567</v>
       </c>
       <c r="E58" s="6">
-        <v>1106.28</v>
+        <v>1105.46</v>
       </c>
       <c r="F58" s="6">
         <v>1217.61</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:15">
       <c r="A59" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B59" s="6">
         <v>507.93</v>
@@ -3440,58 +3602,58 @@
         <v>17</v>
       </c>
       <c r="D59" s="7">
-        <v>1.411257</v>
+        <v>1.410966</v>
       </c>
       <c r="E59" s="6">
-        <v>716.8200000000001</v>
+        <v>716.67</v>
       </c>
       <c r="F59" s="6">
         <v>774.03</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:15">
       <c r="A60" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B60" s="6">
-        <v>423.25</v>
+        <v>423.251</v>
       </c>
       <c r="C60" s="6">
         <v>10</v>
       </c>
       <c r="D60" s="7">
-        <v>1.699894</v>
+        <v>1.698671</v>
       </c>
       <c r="E60" s="6">
-        <v>719.48</v>
+        <v>718.96</v>
       </c>
       <c r="F60" s="6">
         <v>755.3099999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:15">
       <c r="A61" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B61" s="6">
-        <v>204.27</v>
+        <v>204.272</v>
       </c>
       <c r="C61" s="6">
         <v>6</v>
       </c>
       <c r="D61" s="7">
-        <v>1.578548</v>
+        <v>1.577804</v>
       </c>
       <c r="E61" s="6">
-        <v>322.45</v>
+        <v>322.3</v>
       </c>
       <c r="F61" s="6">
         <v>335.69</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:15">
       <c r="A62" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B62" s="6">
         <v>2</v>
@@ -3509,9 +3671,9 @@
         <v>8.98</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:15">
       <c r="A63" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B63" s="6">
         <v>2</v>
@@ -3529,19 +3691,19 @@
         <v>53.66</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:15">
       <c r="A64" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B64" s="9">
-        <v>1786.84</v>
+        <v>1786.841</v>
       </c>
       <c r="C64" s="9">
         <v>52</v>
       </c>
       <c r="D64" s="7"/>
       <c r="E64" s="9">
-        <v>2927.67</v>
+        <v>2926.03</v>
       </c>
       <c r="F64" s="9">
         <v>3145.28</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 2/ДЕМАКС АД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС АД % ГРУПА 2/ДЕМАКС АД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="205">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -639,8 +636,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -733,10 +730,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1031,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1044,13 +1041,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1093,595 +1090,556 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F2">
         <v>29.947</v>
       </c>
       <c r="G2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H2">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I2" s="1">
-        <v>1.389</v>
+        <v>41.596</v>
       </c>
       <c r="J2">
-        <v>41.596383</v>
+        <v>1.52</v>
       </c>
       <c r="K2" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L2" s="1">
-        <v>45.51944</v>
-      </c>
-      <c r="M2" t="s">
-        <v>104</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>45.519</v>
+      </c>
+      <c r="L2" t="s">
+        <v>103</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F3">
         <v>18.22</v>
       </c>
       <c r="G3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H3">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I3" s="1">
-        <v>1.389</v>
+        <v>25.308</v>
       </c>
       <c r="J3">
-        <v>25.30758</v>
+        <v>1.5</v>
       </c>
       <c r="K3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L3" s="1">
         <v>27.33</v>
       </c>
-      <c r="M3" t="s">
-        <v>105</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="L3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F4">
         <v>41.712</v>
       </c>
       <c r="G4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H4">
-        <v>1.619</v>
+        <v>1.699</v>
       </c>
       <c r="I4" s="1">
-        <v>1.699</v>
+        <v>70.869</v>
       </c>
       <c r="J4">
-        <v>70.86868800000001</v>
+        <v>1.77</v>
       </c>
       <c r="K4" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L4" s="1">
-        <v>73.83024</v>
-      </c>
-      <c r="M4" t="s">
-        <v>106</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>73.83</v>
+      </c>
+      <c r="L4" t="s">
+        <v>105</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F5">
         <v>43.861</v>
       </c>
       <c r="G5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H5">
-        <v>1.619</v>
+        <v>1.699</v>
       </c>
       <c r="I5" s="1">
-        <v>1.699</v>
+        <v>74.52</v>
       </c>
       <c r="J5">
-        <v>74.519839</v>
+        <v>1.8</v>
       </c>
       <c r="K5" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="L5" s="1">
-        <v>78.9498</v>
-      </c>
-      <c r="M5" t="s">
-        <v>107</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>78.95</v>
+      </c>
+      <c r="L5" t="s">
+        <v>106</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F6">
         <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H6">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I6" s="1">
-        <v>1.389</v>
+        <v>37.503</v>
       </c>
       <c r="J6">
-        <v>37.503</v>
+        <v>1.5</v>
       </c>
       <c r="K6" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L6" s="1">
         <v>40.5</v>
       </c>
-      <c r="M6" t="s">
-        <v>108</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="L6" t="s">
+        <v>107</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F7">
         <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H7">
-        <v>1.399</v>
+        <v>1.429</v>
       </c>
       <c r="I7" s="1">
-        <v>1.429</v>
+        <v>57.16</v>
       </c>
       <c r="J7">
-        <v>57.16</v>
+        <v>1.51</v>
       </c>
       <c r="K7" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L7" s="1">
         <v>60.4</v>
       </c>
-      <c r="M7" t="s">
-        <v>109</v>
-      </c>
-      <c r="N7">
+      <c r="L7" t="s">
+        <v>108</v>
+      </c>
+      <c r="M7">
         <v>141141</v>
       </c>
-      <c r="O7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F8">
         <v>23.13</v>
       </c>
       <c r="G8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H8">
-        <v>1.619</v>
+        <v>1.699</v>
       </c>
       <c r="I8" s="1">
-        <v>1.699</v>
+        <v>39.298</v>
       </c>
       <c r="J8">
-        <v>39.29787</v>
+        <v>1.77</v>
       </c>
       <c r="K8" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L8" s="1">
-        <v>40.9401</v>
-      </c>
-      <c r="M8" t="s">
-        <v>110</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>40.94</v>
+      </c>
+      <c r="L8" t="s">
+        <v>109</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F9">
         <v>53.352</v>
       </c>
       <c r="G9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H9">
-        <v>1.649</v>
+        <v>1.709</v>
       </c>
       <c r="I9" s="1">
-        <v>1.709</v>
+        <v>91.179</v>
       </c>
       <c r="J9">
-        <v>91.178568</v>
+        <v>1.76</v>
       </c>
       <c r="K9" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L9" s="1">
-        <v>93.89952</v>
-      </c>
-      <c r="M9" t="s">
-        <v>111</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="L9" t="s">
+        <v>110</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F10">
         <v>42.027</v>
       </c>
       <c r="G10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H10">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I10" s="1">
-        <v>1.679</v>
+        <v>70.563</v>
       </c>
       <c r="J10">
-        <v>70.563333</v>
+        <v>1.82</v>
       </c>
       <c r="K10" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="L10" s="1">
-        <v>76.48914000000001</v>
-      </c>
-      <c r="M10" t="s">
-        <v>112</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>76.489</v>
+      </c>
+      <c r="L10" t="s">
+        <v>111</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F11">
         <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H11">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I11" s="1">
-        <v>1.389</v>
+        <v>38.892</v>
       </c>
       <c r="J11">
-        <v>38.892</v>
+        <v>1.49</v>
       </c>
       <c r="K11" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L11" s="1">
         <v>41.72</v>
       </c>
-      <c r="M11" t="s">
-        <v>113</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="L11" t="s">
+        <v>112</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F12">
         <v>22.682</v>
       </c>
       <c r="G12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H12">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I12" s="1">
-        <v>1.389</v>
+        <v>31.505</v>
       </c>
       <c r="J12">
-        <v>31.505298</v>
+        <v>1.51</v>
       </c>
       <c r="K12" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L12" s="1">
-        <v>34.24982</v>
-      </c>
-      <c r="M12" t="s">
-        <v>114</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>34.25</v>
+      </c>
+      <c r="L12" t="s">
+        <v>113</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F13">
         <v>27.822</v>
       </c>
       <c r="G13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H13">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I13" s="1">
-        <v>1.436</v>
+        <v>39.952</v>
       </c>
       <c r="J13">
-        <v>39.952392</v>
+        <v>1.52</v>
       </c>
       <c r="K13" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L13" s="1">
-        <v>42.28944</v>
-      </c>
-      <c r="M13" t="s">
-        <v>115</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>42.289</v>
+      </c>
+      <c r="L13" t="s">
+        <v>114</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H14">
         <v>26.83</v>
@@ -1695,87 +1653,81 @@
       <c r="K14" s="1">
         <v>26.83</v>
       </c>
-      <c r="L14" s="1">
-        <v>26.83</v>
-      </c>
-      <c r="M14" t="s">
-        <v>115</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="L14" t="s">
+        <v>114</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F15">
         <v>25.039</v>
       </c>
       <c r="G15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H15">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I15" s="1">
-        <v>1.436</v>
+        <v>35.956</v>
       </c>
       <c r="J15">
-        <v>35.956004</v>
+        <v>1.52</v>
       </c>
       <c r="K15" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L15" s="1">
-        <v>38.05928</v>
-      </c>
-      <c r="M15" t="s">
-        <v>116</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>38.059</v>
+      </c>
+      <c r="L15" t="s">
+        <v>115</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H16">
         <v>4.49</v>
@@ -1789,181 +1741,169 @@
       <c r="K16" s="1">
         <v>4.49</v>
       </c>
-      <c r="L16" s="1">
-        <v>4.49</v>
-      </c>
-      <c r="M16" t="s">
-        <v>116</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="L16" t="s">
+        <v>115</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F17">
         <v>40.977</v>
       </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H17">
-        <v>1.629</v>
+        <v>1.689</v>
       </c>
       <c r="I17" s="1">
-        <v>1.689</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="J17">
-        <v>69.21015300000001</v>
+        <v>1.76</v>
       </c>
       <c r="K17" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L17" s="1">
-        <v>72.11951999999999</v>
-      </c>
-      <c r="M17" t="s">
-        <v>117</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>72.12</v>
+      </c>
+      <c r="L17" t="s">
+        <v>116</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F18">
         <v>26.293</v>
       </c>
       <c r="G18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H18">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I18" s="1">
-        <v>1.389</v>
+        <v>36.521</v>
       </c>
       <c r="J18">
-        <v>36.520977</v>
+        <v>1.5</v>
       </c>
       <c r="K18" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L18" s="1">
-        <v>39.4395</v>
-      </c>
-      <c r="M18" t="s">
-        <v>118</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>39.439</v>
+      </c>
+      <c r="L18" t="s">
+        <v>117</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F19">
         <v>35</v>
       </c>
       <c r="G19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H19">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I19" s="1">
-        <v>1.679</v>
+        <v>58.765</v>
       </c>
       <c r="J19">
-        <v>58.765</v>
+        <v>1.78</v>
       </c>
       <c r="K19" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L19" s="1">
         <v>62.3</v>
       </c>
-      <c r="M19" t="s">
-        <v>119</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="L19" t="s">
+        <v>118</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H20">
         <v>26.83</v>
@@ -1977,1356 +1917,1269 @@
       <c r="K20" s="1">
         <v>26.83</v>
       </c>
-      <c r="L20" s="1">
-        <v>26.83</v>
-      </c>
-      <c r="M20" t="s">
-        <v>119</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="L20" t="s">
+        <v>118</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F21">
         <v>35.56</v>
       </c>
       <c r="G21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H21">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I21" s="1">
-        <v>1.389</v>
+        <v>49.393</v>
       </c>
       <c r="J21">
-        <v>49.39284</v>
+        <v>1.5</v>
       </c>
       <c r="K21" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L21" s="1">
         <v>53.34</v>
       </c>
-      <c r="M21" t="s">
-        <v>120</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="L21" t="s">
+        <v>119</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F22">
         <v>64.02800000000001</v>
       </c>
       <c r="G22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H22">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I22" s="1">
-        <v>1.679</v>
+        <v>107.503</v>
       </c>
       <c r="J22">
-        <v>107.503012</v>
+        <v>1.8</v>
       </c>
       <c r="K22" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="L22" s="1">
-        <v>115.2504</v>
-      </c>
-      <c r="M22" t="s">
-        <v>121</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>115.25</v>
+      </c>
+      <c r="L22" t="s">
+        <v>120</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F23">
         <v>50.091</v>
       </c>
       <c r="G23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H23">
-        <v>1.629</v>
+        <v>1.689</v>
       </c>
       <c r="I23" s="1">
-        <v>1.689</v>
+        <v>84.604</v>
       </c>
       <c r="J23">
-        <v>84.60369900000001</v>
+        <v>1.76</v>
       </c>
       <c r="K23" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L23" s="1">
-        <v>88.16016</v>
-      </c>
-      <c r="M23" t="s">
-        <v>122</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>88.16</v>
+      </c>
+      <c r="L23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24">
         <v>27.55</v>
       </c>
       <c r="G24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H24">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I24" s="1">
-        <v>1.389</v>
+        <v>38.267</v>
       </c>
       <c r="J24">
-        <v>38.26695</v>
+        <v>1.49</v>
       </c>
       <c r="K24" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L24" s="1">
-        <v>41.0495</v>
-      </c>
-      <c r="M24" t="s">
-        <v>123</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>41.05</v>
+      </c>
+      <c r="L24" t="s">
+        <v>122</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F25">
         <v>46.989</v>
       </c>
       <c r="G25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H25">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I25" s="1">
-        <v>1.679</v>
+        <v>78.895</v>
       </c>
       <c r="J25">
-        <v>78.894531</v>
+        <v>1.82</v>
       </c>
       <c r="K25" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="L25" s="1">
-        <v>85.51998</v>
-      </c>
-      <c r="M25" t="s">
-        <v>124</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>85.52</v>
+      </c>
+      <c r="L25" t="s">
+        <v>123</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F26">
         <v>52.62</v>
       </c>
       <c r="G26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H26">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I26" s="1">
-        <v>1.679</v>
+        <v>88.349</v>
       </c>
       <c r="J26">
-        <v>88.34898</v>
+        <v>1.84</v>
       </c>
       <c r="K26" s="1">
-        <v>1.84</v>
-      </c>
-      <c r="L26" s="1">
-        <v>96.82080000000001</v>
-      </c>
-      <c r="M26" t="s">
-        <v>125</v>
-      </c>
-      <c r="N26">
+        <v>96.821</v>
+      </c>
+      <c r="L26" t="s">
+        <v>124</v>
+      </c>
+      <c r="M26">
         <v>142000</v>
       </c>
-      <c r="O26" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="N26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F27">
         <v>37.762</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H27">
-        <v>1.369</v>
+        <v>1.399</v>
       </c>
       <c r="I27" s="1">
-        <v>1.399</v>
+        <v>52.829</v>
       </c>
       <c r="J27">
-        <v>52.829038</v>
+        <v>1.51</v>
       </c>
       <c r="K27" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L27" s="1">
-        <v>57.02062</v>
-      </c>
-      <c r="M27" t="s">
-        <v>126</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+        <v>57.021</v>
+      </c>
+      <c r="L27" t="s">
+        <v>125</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F28">
         <v>20.74</v>
       </c>
       <c r="G28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H28">
-        <v>1.369</v>
+        <v>1.399</v>
       </c>
       <c r="I28" s="1">
-        <v>1.399</v>
+        <v>29.015</v>
       </c>
       <c r="J28">
-        <v>29.01526</v>
+        <v>1.5</v>
       </c>
       <c r="K28" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L28" s="1">
         <v>31.11</v>
       </c>
-      <c r="M28" t="s">
-        <v>127</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="L28" t="s">
+        <v>126</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F29">
         <v>32.022</v>
       </c>
       <c r="G29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H29">
-        <v>1.629</v>
+        <v>1.689</v>
       </c>
       <c r="I29" s="1">
-        <v>1.689</v>
+        <v>54.085</v>
       </c>
       <c r="J29">
-        <v>54.085158</v>
+        <v>1.78</v>
       </c>
       <c r="K29" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L29" s="1">
-        <v>56.99916</v>
-      </c>
-      <c r="M29" t="s">
-        <v>128</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+        <v>56.999</v>
+      </c>
+      <c r="L29" t="s">
+        <v>127</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F30">
         <v>27.18</v>
       </c>
       <c r="G30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H30">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I30" s="1">
-        <v>1.679</v>
+        <v>45.635</v>
       </c>
       <c r="J30">
-        <v>45.63522</v>
+        <v>1.89</v>
       </c>
       <c r="K30" s="1">
-        <v>1.89</v>
-      </c>
-      <c r="L30" s="1">
-        <v>51.3702</v>
-      </c>
-      <c r="M30" t="s">
-        <v>129</v>
-      </c>
-      <c r="N30">
+        <v>51.37</v>
+      </c>
+      <c r="L30" t="s">
+        <v>128</v>
+      </c>
+      <c r="M30">
         <v>300</v>
       </c>
-      <c r="O30" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="N30" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F31">
         <v>63.418</v>
       </c>
       <c r="G31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H31">
-        <v>1.629</v>
+        <v>1.689</v>
       </c>
       <c r="I31" s="1">
-        <v>1.689</v>
+        <v>107.113</v>
       </c>
       <c r="J31">
-        <v>107.113002</v>
+        <v>1.77</v>
       </c>
       <c r="K31" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L31" s="1">
-        <v>112.24986</v>
-      </c>
-      <c r="M31" t="s">
-        <v>130</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+        <v>112.25</v>
+      </c>
+      <c r="L31" t="s">
+        <v>129</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F32">
         <v>31.568</v>
       </c>
       <c r="G32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H32">
-        <v>1.608</v>
+        <v>1.688</v>
       </c>
       <c r="I32" s="1">
-        <v>1.688</v>
+        <v>53.287</v>
       </c>
       <c r="J32">
-        <v>53.286784</v>
+        <v>1.92</v>
       </c>
       <c r="K32" s="1">
-        <v>1.92</v>
-      </c>
-      <c r="L32" s="1">
-        <v>60.61056</v>
-      </c>
-      <c r="M32" t="s">
-        <v>131</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+        <v>60.611</v>
+      </c>
+      <c r="L32" t="s">
+        <v>130</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F33">
         <v>51.961</v>
       </c>
       <c r="G33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H33">
-        <v>1.629</v>
+        <v>1.689</v>
       </c>
       <c r="I33" s="1">
-        <v>1.689</v>
+        <v>87.762</v>
       </c>
       <c r="J33">
-        <v>87.762129</v>
+        <v>1.79</v>
       </c>
       <c r="K33" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L33" s="1">
-        <v>93.01018999999999</v>
-      </c>
-      <c r="M33" t="s">
-        <v>132</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+        <v>93.01000000000001</v>
+      </c>
+      <c r="L33" t="s">
+        <v>131</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F34">
         <v>23.422</v>
       </c>
       <c r="G34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H34">
-        <v>1.629</v>
+        <v>1.689</v>
       </c>
       <c r="I34" s="1">
-        <v>1.689</v>
+        <v>39.56</v>
       </c>
       <c r="J34">
-        <v>39.559758</v>
+        <v>1.8</v>
       </c>
       <c r="K34" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="L34" s="1">
-        <v>42.1596</v>
-      </c>
-      <c r="M34" t="s">
-        <v>133</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+        <v>42.16</v>
+      </c>
+      <c r="L34" t="s">
+        <v>132</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F35">
         <v>56.711</v>
       </c>
       <c r="G35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H35">
-        <v>1.608</v>
+        <v>1.688</v>
       </c>
       <c r="I35" s="1">
-        <v>1.688</v>
+        <v>95.72799999999999</v>
       </c>
       <c r="J35">
-        <v>95.728168</v>
+        <v>1.94</v>
       </c>
       <c r="K35" s="1">
-        <v>1.94</v>
-      </c>
-      <c r="L35" s="1">
-        <v>110.01934</v>
-      </c>
-      <c r="M35" t="s">
-        <v>134</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+        <v>110.019</v>
+      </c>
+      <c r="L35" t="s">
+        <v>133</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F36">
         <v>32.909</v>
       </c>
       <c r="G36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H36">
-        <v>1.389</v>
+        <v>1.419</v>
       </c>
       <c r="I36" s="1">
-        <v>1.419</v>
+        <v>46.698</v>
       </c>
       <c r="J36">
-        <v>46.697871</v>
+        <v>1.54</v>
       </c>
       <c r="K36" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L36" s="1">
-        <v>50.67986</v>
-      </c>
-      <c r="M36" t="s">
-        <v>135</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+        <v>50.68</v>
+      </c>
+      <c r="L36" t="s">
+        <v>134</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F37">
         <v>24.639</v>
       </c>
       <c r="G37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H37">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I37" s="1">
-        <v>1.431</v>
+        <v>35.258</v>
       </c>
       <c r="J37">
-        <v>35.258409</v>
+        <v>1.55</v>
       </c>
       <c r="K37" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L37" s="1">
-        <v>38.19045</v>
-      </c>
-      <c r="M37" t="s">
-        <v>136</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+        <v>38.19</v>
+      </c>
+      <c r="L37" t="s">
+        <v>135</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F38">
         <v>35.778</v>
       </c>
       <c r="G38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H38">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I38" s="1">
-        <v>1.431</v>
+        <v>51.198</v>
       </c>
       <c r="J38">
-        <v>51.198318</v>
+        <v>1.53</v>
       </c>
       <c r="K38" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L38" s="1">
-        <v>54.74034</v>
-      </c>
-      <c r="M38" t="s">
-        <v>137</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+        <v>54.74</v>
+      </c>
+      <c r="L38" t="s">
+        <v>136</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F39">
         <v>30.363</v>
       </c>
       <c r="G39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H39">
-        <v>1.649</v>
+        <v>1.709</v>
       </c>
       <c r="I39" s="1">
-        <v>1.709</v>
+        <v>51.89</v>
       </c>
       <c r="J39">
-        <v>51.890367</v>
+        <v>1.82</v>
       </c>
       <c r="K39" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="L39" s="1">
-        <v>55.26066</v>
-      </c>
-      <c r="M39" t="s">
-        <v>138</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+        <v>55.261</v>
+      </c>
+      <c r="L39" t="s">
+        <v>137</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F40">
         <v>23.62</v>
       </c>
       <c r="G40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H40">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I40" s="1">
-        <v>1.649</v>
+        <v>38.949</v>
       </c>
       <c r="J40">
-        <v>38.94938</v>
+        <v>1.71</v>
       </c>
       <c r="K40" s="1">
-        <v>1.71</v>
-      </c>
-      <c r="L40" s="1">
-        <v>40.3902</v>
-      </c>
-      <c r="M40" t="s">
-        <v>139</v>
-      </c>
-      <c r="N40">
+        <v>40.39</v>
+      </c>
+      <c r="L40" t="s">
+        <v>138</v>
+      </c>
+      <c r="M40">
         <v>142450</v>
       </c>
-      <c r="O40" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="N40" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F41">
         <v>45.568</v>
       </c>
       <c r="G41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H41">
-        <v>1.649</v>
+        <v>1.709</v>
       </c>
       <c r="I41" s="1">
-        <v>1.709</v>
+        <v>77.876</v>
       </c>
       <c r="J41">
-        <v>77.87571199999999</v>
+        <v>1.83</v>
       </c>
       <c r="K41" s="1">
-        <v>1.83</v>
-      </c>
-      <c r="L41" s="1">
-        <v>83.38943999999999</v>
-      </c>
-      <c r="M41" t="s">
-        <v>140</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+        <v>83.389</v>
+      </c>
+      <c r="L41" t="s">
+        <v>139</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F42">
         <v>19.468</v>
       </c>
       <c r="G42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H42">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I42" s="1">
-        <v>1.431</v>
+        <v>27.859</v>
       </c>
       <c r="J42">
-        <v>27.858708</v>
+        <v>1.54</v>
       </c>
       <c r="K42" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L42" s="1">
-        <v>29.98072</v>
-      </c>
-      <c r="M42" t="s">
-        <v>141</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+        <v>29.981</v>
+      </c>
+      <c r="L42" t="s">
+        <v>140</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F43">
         <v>55.97</v>
       </c>
       <c r="G43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H43">
-        <v>1.648</v>
+        <v>1.728</v>
       </c>
       <c r="I43" s="1">
-        <v>1.728</v>
+        <v>96.71599999999999</v>
       </c>
       <c r="J43">
-        <v>96.71616</v>
+        <v>2</v>
       </c>
       <c r="K43" s="1">
-        <v>2</v>
-      </c>
-      <c r="L43" s="1">
         <v>111.94</v>
       </c>
-      <c r="M43" t="s">
-        <v>142</v>
-      </c>
-      <c r="N43">
+      <c r="L43" t="s">
+        <v>141</v>
+      </c>
+      <c r="M43">
         <v>500</v>
       </c>
-      <c r="O43" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="N43" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F44">
         <v>19.262</v>
       </c>
       <c r="G44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H44">
-        <v>1.648</v>
+        <v>1.728</v>
       </c>
       <c r="I44" s="1">
-        <v>1.728</v>
+        <v>33.285</v>
       </c>
       <c r="J44">
-        <v>33.284736</v>
+        <v>2.02</v>
       </c>
       <c r="K44" s="1">
-        <v>2.02</v>
-      </c>
-      <c r="L44" s="1">
-        <v>38.90924</v>
-      </c>
-      <c r="M44" t="s">
-        <v>143</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+        <v>38.909</v>
+      </c>
+      <c r="L44" t="s">
+        <v>142</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E45" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F45">
         <v>36.173</v>
       </c>
       <c r="G45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H45">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I45" s="1">
-        <v>1.431</v>
+        <v>51.764</v>
       </c>
       <c r="J45">
-        <v>51.763563</v>
+        <v>1.56</v>
       </c>
       <c r="K45" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L45" s="1">
-        <v>56.42988</v>
-      </c>
-      <c r="M45" t="s">
-        <v>144</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+        <v>56.43</v>
+      </c>
+      <c r="L45" t="s">
+        <v>143</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D46" t="s">
+        <v>94</v>
+      </c>
+      <c r="E46" t="s">
         <v>95</v>
-      </c>
-      <c r="E46" t="s">
-        <v>96</v>
       </c>
       <c r="F46">
         <v>65.699</v>
       </c>
       <c r="G46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H46">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I46" s="1">
-        <v>1.431</v>
+        <v>94.015</v>
       </c>
       <c r="J46">
-        <v>94.015269</v>
+        <v>1.56</v>
       </c>
       <c r="K46" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L46" s="1">
-        <v>102.49044</v>
-      </c>
-      <c r="M46" t="s">
-        <v>145</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+        <v>102.49</v>
+      </c>
+      <c r="L46" t="s">
+        <v>144</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D47" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F47">
         <v>51.33</v>
       </c>
       <c r="G47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H47">
-        <v>1.702</v>
+        <v>1.782</v>
       </c>
       <c r="I47" s="1">
-        <v>1.782</v>
+        <v>91.47</v>
       </c>
       <c r="J47">
-        <v>91.47006</v>
+        <v>2</v>
       </c>
       <c r="K47" s="1">
-        <v>2</v>
-      </c>
-      <c r="L47" s="1">
         <v>102.66</v>
       </c>
-      <c r="M47" t="s">
-        <v>146</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="L47" t="s">
+        <v>145</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F48">
         <v>56</v>
       </c>
       <c r="G48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H48">
-        <v>1.716</v>
+        <v>1.796</v>
       </c>
       <c r="I48" s="1">
-        <v>1.796</v>
+        <v>100.576</v>
       </c>
       <c r="J48">
-        <v>100.576</v>
+        <v>2</v>
       </c>
       <c r="K48" s="1">
-        <v>2</v>
-      </c>
-      <c r="L48" s="1">
         <v>112</v>
       </c>
-      <c r="M48" t="s">
-        <v>147</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="L48" t="s">
+        <v>146</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D49" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H49">
         <v>4.49</v>
@@ -3340,210 +3193,195 @@
       <c r="K49" s="1">
         <v>4.49</v>
       </c>
-      <c r="L49" s="1">
-        <v>4.49</v>
-      </c>
-      <c r="M49" t="s">
-        <v>147</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
+      <c r="L49" t="s">
+        <v>146</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F50">
         <v>41.96</v>
       </c>
       <c r="G50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H50">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I50" s="1">
-        <v>1.704</v>
+        <v>71.5</v>
       </c>
       <c r="J50">
-        <v>71.49984000000001</v>
+        <v>1.75</v>
       </c>
       <c r="K50" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L50" s="1">
         <v>73.43000000000001</v>
       </c>
-      <c r="M50" t="s">
-        <v>148</v>
-      </c>
-      <c r="N50">
+      <c r="L50" t="s">
+        <v>147</v>
+      </c>
+      <c r="M50">
         <v>142800</v>
       </c>
-      <c r="O50" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+      <c r="N50" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F51">
         <v>32.077</v>
       </c>
       <c r="G51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H51">
-        <v>1.676</v>
+        <v>1.736</v>
       </c>
       <c r="I51" s="1">
-        <v>1.736</v>
+        <v>55.686</v>
       </c>
       <c r="J51">
-        <v>55.685672</v>
+        <v>1.81</v>
       </c>
       <c r="K51" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="L51" s="1">
-        <v>58.05937</v>
-      </c>
-      <c r="M51" t="s">
-        <v>149</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+        <v>58.059</v>
+      </c>
+      <c r="L51" t="s">
+        <v>148</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F52">
         <v>19.51</v>
       </c>
       <c r="G52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H52">
-        <v>1.459</v>
+        <v>1.489</v>
       </c>
       <c r="I52" s="1">
-        <v>1.489</v>
+        <v>29.05</v>
       </c>
       <c r="J52">
-        <v>29.05039</v>
+        <v>1.55</v>
       </c>
       <c r="K52" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L52" s="1">
-        <v>30.2405</v>
-      </c>
-      <c r="M52" t="s">
-        <v>150</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+        <v>30.241</v>
+      </c>
+      <c r="L52" t="s">
+        <v>149</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F53">
         <v>45.831</v>
       </c>
       <c r="G53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H53">
-        <v>1.689</v>
+        <v>1.719</v>
       </c>
       <c r="I53" s="1">
-        <v>1.719</v>
+        <v>78.783</v>
       </c>
       <c r="J53">
-        <v>78.783489</v>
+        <v>1.77</v>
       </c>
       <c r="K53" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L53" s="1">
-        <v>81.12087</v>
-      </c>
-      <c r="M53" t="s">
-        <v>151</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53" t="s">
+        <v>81.121</v>
+      </c>
+      <c r="L53" t="s">
+        <v>150</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" s="3" t="s">
         <v>199</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
-      <c r="A56" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -3551,149 +3389,149 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:14">
       <c r="A57" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="C57" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="D57" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>204</v>
-      </c>
       <c r="E57" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B58" s="6">
         <v>647.388</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="7">
         <v>15</v>
       </c>
       <c r="D58" s="7">
-        <v>1.707567</v>
-      </c>
-      <c r="E58" s="6">
-        <v>1105.46</v>
-      </c>
-      <c r="F58" s="6">
-        <v>1217.61</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
+        <v>1.708</v>
+      </c>
+      <c r="E58" s="7">
+        <v>1105.459</v>
+      </c>
+      <c r="F58" s="7">
+        <v>1217.609</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B59" s="6">
         <v>507.93</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="7">
         <v>17</v>
       </c>
       <c r="D59" s="7">
-        <v>1.410966</v>
-      </c>
-      <c r="E59" s="6">
-        <v>716.67</v>
-      </c>
-      <c r="F59" s="6">
-        <v>774.03</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+        <v>1.411</v>
+      </c>
+      <c r="E59" s="7">
+        <v>716.671</v>
+      </c>
+      <c r="F59" s="7">
+        <v>774.0309999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B60" s="6">
         <v>423.251</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="7">
         <v>10</v>
       </c>
       <c r="D60" s="7">
-        <v>1.698671</v>
-      </c>
-      <c r="E60" s="6">
-        <v>718.96</v>
-      </c>
-      <c r="F60" s="6">
-        <v>755.3099999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
+        <v>1.699</v>
+      </c>
+      <c r="E60" s="7">
+        <v>718.965</v>
+      </c>
+      <c r="F60" s="7">
+        <v>755.308</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B61" s="6">
         <v>204.272</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="7">
         <v>6</v>
       </c>
       <c r="D61" s="7">
-        <v>1.577804</v>
-      </c>
-      <c r="E61" s="6">
+        <v>1.578</v>
+      </c>
+      <c r="E61" s="7">
         <v>322.3</v>
       </c>
-      <c r="F61" s="6">
-        <v>335.69</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15">
+      <c r="F61" s="7">
+        <v>335.689</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B62" s="6">
         <v>2</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="7">
         <v>2</v>
       </c>
       <c r="D62" s="7">
         <v>4.49</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E62" s="7">
         <v>8.98</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F62" s="7">
         <v>8.98</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:14">
       <c r="A63" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B63" s="6">
         <v>2</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63" s="7">
         <v>2</v>
       </c>
       <c r="D63" s="7">
         <v>26.83</v>
       </c>
-      <c r="E63" s="6">
+      <c r="E63" s="7">
         <v>53.66</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F63" s="7">
         <v>53.66</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:14">
       <c r="A64" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B64" s="9">
         <v>1786.841</v>
@@ -3703,10 +3541,10 @@
       </c>
       <c r="D64" s="7"/>
       <c r="E64" s="9">
-        <v>2926.03</v>
+        <v>2926.035</v>
       </c>
       <c r="F64" s="9">
-        <v>3145.28</v>
+        <v>3145.277</v>
       </c>
     </row>
   </sheetData>
